--- a/public/exports/29189404.xlsx
+++ b/public/exports/29189404.xlsx
@@ -181,7 +181,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100072983</t>
+          <t xml:space="preserve">100078592</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -190,7 +190,7 @@
         </is>
       </c>
       <c r="F4">
-        <v>280</v>
+        <v>323</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -236,11 +236,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F5">
-        <v>323</v>
+        <v>288</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -286,11 +286,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F6">
-        <v>288</v>
+        <v>473</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">100078592</t>
+          <t xml:space="preserve">100096939</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F7">
-        <v>473</v>
+        <v>660</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">100096939</t>
+          <t xml:space="preserve">100101318</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F8">
-        <v>660</v>
+        <v>330</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">100101318</t>
+          <t xml:space="preserve">100197946</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F9">
-        <v>330</v>
+        <v>392</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">100197946</t>
+          <t xml:space="preserve">100513809</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="F10">
-        <v>392</v>
+        <v>2037</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513809</t>
+          <t xml:space="preserve">100513810</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F11">
-        <v>2037</v>
+        <v>2429</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513810</t>
+          <t xml:space="preserve">100513811</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="F12">
-        <v>2429</v>
+        <v>252</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513811</t>
+          <t xml:space="preserve">100513812</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F13">
-        <v>252</v>
+        <v>1728</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513812</t>
+          <t xml:space="preserve">100513815</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="F14">
-        <v>1728</v>
+        <v>475</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513815</t>
+          <t xml:space="preserve">100513816</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F15">
-        <v>475</v>
+        <v>1204</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513816</t>
+          <t xml:space="preserve">100513819</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">117</t>
         </is>
       </c>
       <c r="F16">
-        <v>1204</v>
+        <v>4873</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513819</t>
+          <t xml:space="preserve">100513820</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">117</t>
+          <t xml:space="preserve">128</t>
         </is>
       </c>
       <c r="F17">
-        <v>4873</v>
+        <v>463</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513820</t>
+          <t xml:space="preserve">100513821</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">128</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F18">
-        <v>463</v>
+        <v>566</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513821</t>
+          <t xml:space="preserve">100513822</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">118</t>
         </is>
       </c>
       <c r="F19">
-        <v>566</v>
+        <v>637</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513822</t>
+          <t xml:space="preserve">100513824</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">118</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="F20">
-        <v>637</v>
+        <v>280</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513824</t>
+          <t xml:space="preserve">1352513</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F21">
-        <v>280</v>
+        <v>525</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352513</t>
+          <t xml:space="preserve">1352516</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="F22">
-        <v>525</v>
+        <v>590</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352516</t>
+          <t xml:space="preserve">2167528</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="F23">
-        <v>590</v>
+        <v>444</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167528</t>
+          <t xml:space="preserve">2167800</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="F24">
-        <v>444</v>
+        <v>337</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167800</t>
+          <t xml:space="preserve">2171273</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="F25">
-        <v>337</v>
+        <v>300</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2170239</t>
+          <t xml:space="preserve">2172704</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F26">
-        <v>640</v>
+        <v>469</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,16 +1331,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2171273</t>
+          <t xml:space="preserve">2172718</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F27">
-        <v>300</v>
+        <v>1318</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172704</t>
+          <t xml:space="preserve">2174609</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F28">
-        <v>469</v>
+        <v>313</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,16 +1431,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172718</t>
+          <t xml:space="preserve">2175641</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F29">
-        <v>1318</v>
+        <v>397</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174609</t>
+          <t xml:space="preserve">2175645</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F30">
-        <v>313</v>
+        <v>565</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,16 +1531,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2175641</t>
+          <t xml:space="preserve">2176798</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F31">
-        <v>397</v>
+        <v>445</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1581,16 +1581,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2175645</t>
+          <t xml:space="preserve">2177368</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F32">
-        <v>565</v>
+        <v>987</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1631,16 +1631,16 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2176798</t>
+          <t xml:space="preserve">2209116</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F33">
-        <v>445</v>
+        <v>342</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1681,16 +1681,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2177368</t>
+          <t xml:space="preserve">2213458</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F34">
-        <v>987</v>
+        <v>295</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1731,16 +1731,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2178448</t>
+          <t xml:space="preserve">2213556</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F35">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1781,16 +1781,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2208892</t>
+          <t xml:space="preserve">2213556</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F36">
-        <v>770</v>
+        <v>469</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,16 +1831,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209116</t>
+          <t xml:space="preserve">2217131</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F37">
-        <v>342</v>
+        <v>866</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1881,16 +1881,16 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213458</t>
+          <t xml:space="preserve">2217717</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F38">
-        <v>295</v>
+        <v>586</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1931,16 +1931,16 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213556</t>
+          <t xml:space="preserve">2217717</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F39">
-        <v>335</v>
+        <v>2746</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1981,16 +1981,16 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213556</t>
+          <t xml:space="preserve">258624, 258625</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F40">
-        <v>469</v>
+        <v>4232</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2031,16 +2031,16 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217131</t>
+          <t xml:space="preserve">271130, 271131</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F41">
-        <v>866</v>
+        <v>13568</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217717</t>
+          <t xml:space="preserve">5303635</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="F42">
-        <v>586</v>
+        <v>632</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2131,16 +2131,16 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217717</t>
+          <t xml:space="preserve">5304088</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F43">
-        <v>2746</v>
+        <v>852</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2181,16 +2181,16 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">271130, 271131</t>
+          <t xml:space="preserve">5304129</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F44">
-        <v>13568</v>
+        <v>394</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303635</t>
+          <t xml:space="preserve">5304824</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="F45">
-        <v>632</v>
+        <v>254</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2281,16 +2281,16 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304088</t>
+          <t xml:space="preserve">5304873</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F46">
-        <v>852</v>
+        <v>1000</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304129</t>
+          <t xml:space="preserve">5305072</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="F47">
-        <v>394</v>
+        <v>322</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304824</t>
+          <t xml:space="preserve">5305533</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="F48">
-        <v>254</v>
+        <v>912</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2431,16 +2431,16 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304873</t>
+          <t xml:space="preserve">5308146</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F49">
-        <v>1000</v>
+        <v>1740</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2481,16 +2481,16 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5305072</t>
+          <t xml:space="preserve">5308146</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F50">
-        <v>322</v>
+        <v>350</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2531,16 +2531,16 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5305533</t>
+          <t xml:space="preserve">5308164</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">73</t>
         </is>
       </c>
       <c r="F51">
-        <v>912</v>
+        <v>462</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2581,16 +2581,16 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308146</t>
+          <t xml:space="preserve">5308164</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">74</t>
         </is>
       </c>
       <c r="F52">
-        <v>1740</v>
+        <v>5006</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2631,16 +2631,16 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308146</t>
+          <t xml:space="preserve">5308263</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F53">
-        <v>350</v>
+        <v>661</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2681,16 +2681,16 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308164</t>
+          <t xml:space="preserve">5308734</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">73</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F54">
-        <v>462</v>
+        <v>3208</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2731,16 +2731,16 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308164</t>
+          <t xml:space="preserve">5308734</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">74</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F55">
-        <v>5006</v>
+        <v>291</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2781,16 +2781,16 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308263</t>
+          <t xml:space="preserve">5308734</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F56">
-        <v>661</v>
+        <v>1747</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308584</t>
+          <t xml:space="preserve">5308734</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="F57">
-        <v>497</v>
+        <v>291</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,11 +2886,11 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F58">
-        <v>3208</v>
+        <v>307</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2936,11 +2936,11 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F59">
-        <v>291</v>
+        <v>261</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2986,11 +2986,11 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F60">
-        <v>1747</v>
+        <v>883</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3031,16 +3031,16 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308734</t>
+          <t xml:space="preserve">5309842</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F61">
-        <v>291</v>
+        <v>4510</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3081,16 +3081,16 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308734</t>
+          <t xml:space="preserve">5313168</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F62">
-        <v>307</v>
+        <v>819</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3131,16 +3131,16 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308734</t>
+          <t xml:space="preserve">719160, 5308146</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F63">
-        <v>261</v>
+        <v>1956</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3181,16 +3181,16 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308734</t>
+          <t xml:space="preserve">719167, 100093183</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F64">
-        <v>883</v>
+        <v>1068</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3231,16 +3231,16 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5309842</t>
+          <t xml:space="preserve">719167, 100093183</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F65">
-        <v>4510</v>
+        <v>1068</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3281,16 +3281,16 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312015</t>
+          <t xml:space="preserve">719175, 5305606</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">139</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F66">
-        <v>20718</v>
+        <v>1440</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3331,16 +3331,16 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312664, 100884612</t>
+          <t xml:space="preserve">719194, 2209303</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F67">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5313168</t>
+          <t xml:space="preserve">719209, 8934795</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F68">
-        <v>819</v>
+        <v>400</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3431,16 +3431,16 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">719145, 100067704</t>
+          <t xml:space="preserve">719209, 8934795</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F69">
-        <v>3529</v>
+        <v>1980</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3481,16 +3481,16 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">719160, 5308146</t>
+          <t xml:space="preserve">719209, 8934795</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F70">
-        <v>1956</v>
+        <v>296</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3531,16 +3531,16 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">719167, 100093183</t>
+          <t xml:space="preserve">719209, 8934795</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F71">
-        <v>1068</v>
+        <v>318</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3581,16 +3581,16 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">719167, 100093183</t>
+          <t xml:space="preserve">719219, 5307564</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F72">
-        <v>1068</v>
+        <v>3050</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">719175, 5305606</t>
+          <t xml:space="preserve">719262, 9232188</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="F73">
-        <v>1440</v>
+        <v>440</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3681,16 +3681,16 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">719194, 2209303</t>
+          <t xml:space="preserve">719268, 5308429</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F74">
-        <v>348</v>
+        <v>266</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3731,16 +3731,16 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">719209, 8934795</t>
+          <t xml:space="preserve">719295, 8907547</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F75">
-        <v>400</v>
+        <v>294</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3781,16 +3781,16 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">719209, 8934795</t>
+          <t xml:space="preserve">719337, 9604964</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F76">
-        <v>1980</v>
+        <v>662</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3831,16 +3831,16 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">719209, 8934795</t>
+          <t xml:space="preserve">7343272</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F77">
-        <v>296</v>
+        <v>1379</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3881,16 +3881,16 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">719209, 8934795</t>
+          <t xml:space="preserve">7969204</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F78">
-        <v>318</v>
+        <v>1000</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3931,16 +3931,16 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">719219, 5307564</t>
+          <t xml:space="preserve">8173183</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F79">
-        <v>3050</v>
+        <v>1867</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3981,16 +3981,16 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">719221</t>
+          <t xml:space="preserve">8173183</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F80">
-        <v>482</v>
+        <v>1260</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4031,16 +4031,16 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">719262, 9232188</t>
+          <t xml:space="preserve">8173183</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F81">
-        <v>440</v>
+        <v>1323</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">719268, 5308429</t>
+          <t xml:space="preserve">8245209</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="F82">
-        <v>266</v>
+        <v>764</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4131,16 +4131,16 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">719290, 100013803</t>
+          <t xml:space="preserve">8377662</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F83">
-        <v>276</v>
+        <v>553</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4181,16 +4181,16 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">719295, 8907547</t>
+          <t xml:space="preserve">8908094</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F84">
-        <v>294</v>
+        <v>692</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">719337, 9604964</t>
+          <t xml:space="preserve">8919779</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="F85">
-        <v>662</v>
+        <v>472</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">7343272</t>
+          <t xml:space="preserve">8995636</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="F86">
-        <v>1379</v>
+        <v>405</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4331,16 +4331,16 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">7969204</t>
+          <t xml:space="preserve">9604965</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F87">
-        <v>1000</v>
+        <v>622</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4381,16 +4381,16 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">8173183</t>
+          <t xml:space="preserve">9883833</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F88">
-        <v>1867</v>
+        <v>378</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4431,16 +4431,16 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">8173183</t>
+          <t xml:space="preserve">9888274</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F89">
-        <v>1260</v>
+        <v>1776</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4481,16 +4481,16 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">8173183</t>
+          <t xml:space="preserve">9888274</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F90">
-        <v>1323</v>
+        <v>788</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">8245209</t>
+          <t xml:space="preserve">2170375</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4540,21 +4540,21 @@
         </is>
       </c>
       <c r="F91">
-        <v>764</v>
+        <v>290</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200014100</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-05-27</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">8377662</t>
+          <t xml:space="preserve">2209116</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4590,21 +4590,21 @@
         </is>
       </c>
       <c r="F92">
-        <v>553</v>
+        <v>671</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200014098</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-05-27</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8908094</t>
+          <t xml:space="preserve">5304764</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4640,21 +4640,21 @@
         </is>
       </c>
       <c r="F93">
-        <v>692</v>
+        <v>709</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200014102</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-05-27</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -4681,30 +4681,30 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">8919779</t>
+          <t xml:space="preserve">8995819</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F94">
-        <v>472</v>
+        <v>1270</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200014099</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-05-27</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">8934798</t>
+          <t xml:space="preserve">2173125</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4740,21 +4740,21 @@
         </is>
       </c>
       <c r="F95">
-        <v>1378</v>
+        <v>508</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200016734</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-01</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995636</t>
+          <t xml:space="preserve">2213439</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4790,21 +4790,21 @@
         </is>
       </c>
       <c r="F96">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200016718</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-01</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">9306000</t>
+          <t xml:space="preserve">2213439</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4840,21 +4840,21 @@
         </is>
       </c>
       <c r="F97">
-        <v>3994</v>
+        <v>313</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200016713</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-01</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -4881,30 +4881,30 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">9604965</t>
+          <t xml:space="preserve">5306188</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F98">
-        <v>622</v>
+        <v>351</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200016729</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-01</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -4931,30 +4931,30 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9808161</t>
+          <t xml:space="preserve">7516035</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F99">
-        <v>821</v>
+        <v>950</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200016725</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-01</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">9883833</t>
+          <t xml:space="preserve">8727425</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4990,21 +4990,21 @@
         </is>
       </c>
       <c r="F100">
-        <v>378</v>
+        <v>796</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200017082</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-07</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">9888274</t>
+          <t xml:space="preserve">9977521</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5040,21 +5040,21 @@
         </is>
       </c>
       <c r="F101">
-        <v>1776</v>
+        <v>940</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200017379</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-10</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5081,30 +5081,30 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">9888274</t>
+          <t xml:space="preserve">2172727</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F102">
-        <v>788</v>
+        <v>747</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200017861</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-23</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9977521</t>
+          <t xml:space="preserve">2172775</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5140,21 +5140,21 @@
         </is>
       </c>
       <c r="F103">
-        <v>940</v>
+        <v>598</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200017862</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-23</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2170375</t>
+          <t xml:space="preserve">2172779</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5190,16 +5190,16 @@
         </is>
       </c>
       <c r="F104">
-        <v>290</v>
+        <v>703</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014100</t>
+          <t xml:space="preserve">200017863</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-27</t>
+          <t xml:space="preserve">2019-07-23</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209116</t>
+          <t xml:space="preserve">2175063</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5240,16 +5240,16 @@
         </is>
       </c>
       <c r="F105">
-        <v>671</v>
+        <v>470</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014098</t>
+          <t xml:space="preserve">200017872</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-27</t>
+          <t xml:space="preserve">2019-07-23</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304764</t>
+          <t xml:space="preserve">8288838</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5290,16 +5290,16 @@
         </is>
       </c>
       <c r="F106">
-        <v>709</v>
+        <v>586</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014102</t>
+          <t xml:space="preserve">200017864</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-27</t>
+          <t xml:space="preserve">2019-07-23</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995819</t>
+          <t xml:space="preserve">2174435</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5340,16 +5340,16 @@
         </is>
       </c>
       <c r="F107">
-        <v>1270</v>
+        <v>814</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014099</t>
+          <t xml:space="preserve">200017906</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-27</t>
+          <t xml:space="preserve">2019-07-24</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2173125</t>
+          <t xml:space="preserve">5304267</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5390,16 +5390,16 @@
         </is>
       </c>
       <c r="F108">
-        <v>508</v>
+        <v>327</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016734</t>
+          <t xml:space="preserve">200017925</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-01</t>
+          <t xml:space="preserve">2019-07-24</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213439</t>
+          <t xml:space="preserve">8995859</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5440,16 +5440,16 @@
         </is>
       </c>
       <c r="F109">
-        <v>392</v>
+        <v>1843</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016718</t>
+          <t xml:space="preserve">200017965</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-01</t>
+          <t xml:space="preserve">2019-07-27</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5481,25 +5481,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213439</t>
+          <t xml:space="preserve">2181467</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F110">
-        <v>313</v>
+        <v>615</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016713</t>
+          <t xml:space="preserve">200018663</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-01</t>
+          <t xml:space="preserve">2019-08-13</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306188</t>
+          <t xml:space="preserve">5304625</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5540,16 +5540,16 @@
         </is>
       </c>
       <c r="F111">
-        <v>351</v>
+        <v>847</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016729</t>
+          <t xml:space="preserve">200018662</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-01</t>
+          <t xml:space="preserve">2019-08-13</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">7516035</t>
+          <t xml:space="preserve">5312134</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5590,16 +5590,16 @@
         </is>
       </c>
       <c r="F112">
-        <v>950</v>
+        <v>965</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016725</t>
+          <t xml:space="preserve">200018671</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-01</t>
+          <t xml:space="preserve">2019-08-13</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8727425</t>
+          <t xml:space="preserve">8040594</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5640,16 +5640,16 @@
         </is>
       </c>
       <c r="F113">
-        <v>796</v>
+        <v>750</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017082</t>
+          <t xml:space="preserve">200018664</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-07</t>
+          <t xml:space="preserve">2019-08-13</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172727</t>
+          <t xml:space="preserve">8971417</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5690,16 +5690,16 @@
         </is>
       </c>
       <c r="F114">
-        <v>747</v>
+        <v>525</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017861</t>
+          <t xml:space="preserve">200018668</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-23</t>
+          <t xml:space="preserve">2019-08-13</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172775</t>
+          <t xml:space="preserve">8995933</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5740,16 +5740,16 @@
         </is>
       </c>
       <c r="F115">
-        <v>598</v>
+        <v>872</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017862</t>
+          <t xml:space="preserve">200018666</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-23</t>
+          <t xml:space="preserve">2019-08-13</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172779</t>
+          <t xml:space="preserve">9113192</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5790,16 +5790,16 @@
         </is>
       </c>
       <c r="F116">
-        <v>703</v>
+        <v>590</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017863</t>
+          <t xml:space="preserve">200018667</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-23</t>
+          <t xml:space="preserve">2019-08-13</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2175063</t>
+          <t xml:space="preserve">10036944</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5840,16 +5840,16 @@
         </is>
       </c>
       <c r="F117">
-        <v>470</v>
+        <v>899</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017872</t>
+          <t xml:space="preserve">200020248</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-23</t>
+          <t xml:space="preserve">2019-09-10</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">8288838</t>
+          <t xml:space="preserve">8225803</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5890,16 +5890,16 @@
         </is>
       </c>
       <c r="F118">
-        <v>586</v>
+        <v>414</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017864</t>
+          <t xml:space="preserve">200020461</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-23</t>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174435</t>
+          <t xml:space="preserve">2167811</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5940,16 +5940,16 @@
         </is>
       </c>
       <c r="F119">
-        <v>814</v>
+        <v>372</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017906</t>
+          <t xml:space="preserve">200020826</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-24</t>
+          <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304267</t>
+          <t xml:space="preserve">2176798</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5990,16 +5990,16 @@
         </is>
       </c>
       <c r="F120">
-        <v>327</v>
+        <v>253</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017925</t>
+          <t xml:space="preserve">200020773</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-24</t>
+          <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995859</t>
+          <t xml:space="preserve">2178666</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="F121">
-        <v>1843</v>
+        <v>479</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017965</t>
+          <t xml:space="preserve">200020771</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-27</t>
+          <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2181467</t>
+          <t xml:space="preserve">2180449</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6090,16 +6090,16 @@
         </is>
       </c>
       <c r="F122">
-        <v>615</v>
+        <v>403</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018663</t>
+          <t xml:space="preserve">200020831</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-13</t>
+          <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304625</t>
+          <t xml:space="preserve">2211212</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6140,16 +6140,16 @@
         </is>
       </c>
       <c r="F123">
-        <v>847</v>
+        <v>372</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018662</t>
+          <t xml:space="preserve">200020775</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-13</t>
+          <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6181,25 +6181,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312134</t>
+          <t xml:space="preserve">2213458</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F124">
-        <v>965</v>
+        <v>311</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018671</t>
+          <t xml:space="preserve">200020830</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-13</t>
+          <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040594</t>
+          <t xml:space="preserve">2216626</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6240,16 +6240,16 @@
         </is>
       </c>
       <c r="F125">
-        <v>750</v>
+        <v>555</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018664</t>
+          <t xml:space="preserve">200020779</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-13</t>
+          <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">8971417</t>
+          <t xml:space="preserve">5304862</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6290,16 +6290,16 @@
         </is>
       </c>
       <c r="F126">
-        <v>525</v>
+        <v>922</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018668</t>
+          <t xml:space="preserve">200020780</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-13</t>
+          <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995933</t>
+          <t xml:space="preserve">5310765</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="F127">
-        <v>872</v>
+        <v>733</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018666</t>
+          <t xml:space="preserve">200020827</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-13</t>
+          <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9113192</t>
+          <t xml:space="preserve">7940083</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -6390,16 +6390,16 @@
         </is>
       </c>
       <c r="F128">
-        <v>590</v>
+        <v>601</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018667</t>
+          <t xml:space="preserve">200020777</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-13</t>
+          <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">10036944</t>
+          <t xml:space="preserve">8948799</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -6440,16 +6440,16 @@
         </is>
       </c>
       <c r="F129">
-        <v>899</v>
+        <v>581</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020248</t>
+          <t xml:space="preserve">200020772</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-10</t>
+          <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225803</t>
+          <t xml:space="preserve">9044555</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -6490,16 +6490,16 @@
         </is>
       </c>
       <c r="F130">
-        <v>414</v>
+        <v>1015</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020461</t>
+          <t xml:space="preserve">200020789</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167811</t>
+          <t xml:space="preserve">9604963</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -6540,11 +6540,11 @@
         </is>
       </c>
       <c r="F131">
-        <v>372</v>
+        <v>879</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020826</t>
+          <t xml:space="preserve">200020787</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6581,20 +6581,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2176798</t>
+          <t xml:space="preserve">9808161</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F132">
-        <v>253</v>
+        <v>821</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020773</t>
+          <t xml:space="preserve">200020781</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2178666</t>
+          <t xml:space="preserve">2172733</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -6640,16 +6640,16 @@
         </is>
       </c>
       <c r="F133">
-        <v>479</v>
+        <v>407</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020771</t>
+          <t xml:space="preserve">200023413</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-21</t>
+          <t xml:space="preserve">2019-11-04</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2180449</t>
+          <t xml:space="preserve">2174559</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6690,16 +6690,16 @@
         </is>
       </c>
       <c r="F134">
-        <v>403</v>
+        <v>611</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020831</t>
+          <t xml:space="preserve">200023817</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-21</t>
+          <t xml:space="preserve">2019-11-12</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6731,25 +6731,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211212</t>
+          <t xml:space="preserve">2209470</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F135">
-        <v>372</v>
+        <v>795</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020775</t>
+          <t xml:space="preserve">200023864</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-21</t>
+          <t xml:space="preserve">2019-11-12</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6781,25 +6781,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213458</t>
+          <t xml:space="preserve">5306607</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F136">
-        <v>311</v>
+        <v>423</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020830</t>
+          <t xml:space="preserve">200023835</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-21</t>
+          <t xml:space="preserve">2019-11-12</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216626</t>
+          <t xml:space="preserve">7054261</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -6840,16 +6840,16 @@
         </is>
       </c>
       <c r="F137">
-        <v>555</v>
+        <v>796</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020779</t>
+          <t xml:space="preserve">200023841</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-21</t>
+          <t xml:space="preserve">2019-11-12</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6881,25 +6881,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304862</t>
+          <t xml:space="preserve">719221</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="F138">
-        <v>922</v>
+        <v>482</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020780</t>
+          <t xml:space="preserve">200023819</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-21</t>
+          <t xml:space="preserve">2019-11-12</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5310765</t>
+          <t xml:space="preserve">7568845</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -6940,16 +6940,16 @@
         </is>
       </c>
       <c r="F139">
-        <v>733</v>
+        <v>354</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020827</t>
+          <t xml:space="preserve">200023910</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-21</t>
+          <t xml:space="preserve">2019-11-13</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">7940083</t>
+          <t xml:space="preserve">2217322</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -6990,16 +6990,16 @@
         </is>
       </c>
       <c r="F140">
-        <v>601</v>
+        <v>293</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020777</t>
+          <t xml:space="preserve">200024857</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-21</t>
+          <t xml:space="preserve">2019-12-01</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7031,25 +7031,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948799</t>
+          <t xml:space="preserve">2217322</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F141">
-        <v>581</v>
+        <v>392</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020772</t>
+          <t xml:space="preserve">200024857</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-21</t>
+          <t xml:space="preserve">2019-12-01</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9044555</t>
+          <t xml:space="preserve">8550293</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -7090,16 +7090,16 @@
         </is>
       </c>
       <c r="F142">
-        <v>1015</v>
+        <v>812</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020789</t>
+          <t xml:space="preserve">200024855</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-21</t>
+          <t xml:space="preserve">2019-12-01</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">9604963</t>
+          <t xml:space="preserve">9113193</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -7140,16 +7140,16 @@
         </is>
       </c>
       <c r="F143">
-        <v>879</v>
+        <v>722</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020787</t>
+          <t xml:space="preserve">200024858</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-21</t>
+          <t xml:space="preserve">2019-12-01</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172733</t>
+          <t xml:space="preserve">5306255</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -7190,16 +7190,16 @@
         </is>
       </c>
       <c r="F144">
-        <v>407</v>
+        <v>1225</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023413</t>
+          <t xml:space="preserve">200024872</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-04</t>
+          <t xml:space="preserve">2019-12-02</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174559</t>
+          <t xml:space="preserve">2178710</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -7240,16 +7240,16 @@
         </is>
       </c>
       <c r="F145">
-        <v>611</v>
+        <v>263</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023817</t>
+          <t xml:space="preserve">200024953</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-12</t>
+          <t xml:space="preserve">2019-12-03</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7281,25 +7281,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209470</t>
+          <t xml:space="preserve">5307880</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F146">
-        <v>795</v>
+        <v>1383</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023864</t>
+          <t xml:space="preserve">200024956</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-12</t>
+          <t xml:space="preserve">2019-12-03</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306607</t>
+          <t xml:space="preserve">8717244</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -7340,16 +7340,16 @@
         </is>
       </c>
       <c r="F147">
-        <v>423</v>
+        <v>1298</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023835</t>
+          <t xml:space="preserve">200024948</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-12</t>
+          <t xml:space="preserve">2019-12-03</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7381,25 +7381,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">7054261</t>
+          <t xml:space="preserve">5308364</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F148">
-        <v>796</v>
+        <v>852</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023841</t>
+          <t xml:space="preserve">200024993</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-12</t>
+          <t xml:space="preserve">2019-12-04</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">7568845</t>
+          <t xml:space="preserve">7896055</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -7440,16 +7440,16 @@
         </is>
       </c>
       <c r="F149">
-        <v>354</v>
+        <v>680</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023910</t>
+          <t xml:space="preserve">200024994</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-13</t>
+          <t xml:space="preserve">2019-12-04</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7481,25 +7481,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217322</t>
+          <t xml:space="preserve">5308151</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F150">
-        <v>293</v>
+        <v>400</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024857</t>
+          <t xml:space="preserve">200027969</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-01</t>
+          <t xml:space="preserve">2020-02-11</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7531,25 +7531,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217322</t>
+          <t xml:space="preserve">8995659</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F151">
-        <v>392</v>
+        <v>995</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024857</t>
+          <t xml:space="preserve">200030999</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-01</t>
+          <t xml:space="preserve">2020-05-03</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550293</t>
+          <t xml:space="preserve">5307587</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -7590,16 +7590,16 @@
         </is>
       </c>
       <c r="F152">
-        <v>812</v>
+        <v>1934</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024855</t>
+          <t xml:space="preserve">200038312</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-01</t>
+          <t xml:space="preserve">2020-10-01</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">9113193</t>
+          <t xml:space="preserve">5308975</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -7640,16 +7640,16 @@
         </is>
       </c>
       <c r="F153">
-        <v>722</v>
+        <v>4292</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024858</t>
+          <t xml:space="preserve">200049549</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-01</t>
+          <t xml:space="preserve">2021-05-26</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306255</t>
+          <t xml:space="preserve">5304086</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -7690,16 +7690,16 @@
         </is>
       </c>
       <c r="F154">
-        <v>1225</v>
+        <v>1906</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024872</t>
+          <t xml:space="preserve">200050785</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-02</t>
+          <t xml:space="preserve">2021-06-29</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7731,25 +7731,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2178710</t>
+          <t xml:space="preserve">2208892</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F155">
-        <v>263</v>
+        <v>770</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024953</t>
+          <t xml:space="preserve">100235815</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-03</t>
+          <t xml:space="preserve">2021-08-03</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307880</t>
+          <t xml:space="preserve">5307061</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -7790,16 +7790,16 @@
         </is>
       </c>
       <c r="F156">
-        <v>1383</v>
+        <v>573</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024956</t>
+          <t xml:space="preserve">200057196</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-03</t>
+          <t xml:space="preserve">2022-02-06</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">8717244</t>
+          <t xml:space="preserve">8135053</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -7840,16 +7840,16 @@
         </is>
       </c>
       <c r="F157">
-        <v>1298</v>
+        <v>9546</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024948</t>
+          <t xml:space="preserve">200057529</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-03</t>
+          <t xml:space="preserve">2022-02-20</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7881,25 +7881,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">10229610</t>
+          <t xml:space="preserve">2172718</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F158">
-        <v>620</v>
+        <v>1898</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025010</t>
+          <t xml:space="preserve">200057621</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-04</t>
+          <t xml:space="preserve">2022-02-23</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7931,25 +7931,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">10229610</t>
+          <t xml:space="preserve">7938930</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F159">
-        <v>1226</v>
+        <v>638</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025010</t>
+          <t xml:space="preserve">200060567</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-04</t>
+          <t xml:space="preserve">2022-06-29</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7981,25 +7981,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308364</t>
+          <t xml:space="preserve">2179645</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F160">
-        <v>852</v>
+        <v>677</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024993</t>
+          <t xml:space="preserve">311052501</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-04</t>
+          <t xml:space="preserve">2024-05-06</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8031,25 +8031,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">7896055</t>
+          <t xml:space="preserve">10229610</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F161">
-        <v>680</v>
+        <v>620</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024994</t>
+          <t xml:space="preserve">311060924</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-04</t>
+          <t xml:space="preserve">2024-06-23</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308151</t>
+          <t xml:space="preserve">10229610</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F162">
-        <v>400</v>
+        <v>1226</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027969</t>
+          <t xml:space="preserve">311060924</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-11</t>
+          <t xml:space="preserve">2024-06-23</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8131,25 +8131,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995659</t>
+          <t xml:space="preserve">2178448</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F163">
-        <v>995</v>
+        <v>322</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030999</t>
+          <t xml:space="preserve">311062021</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-03</t>
+          <t xml:space="preserve">2024-06-27</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307587</t>
+          <t xml:space="preserve">2174626</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -8190,16 +8190,16 @@
         </is>
       </c>
       <c r="F164">
-        <v>1934</v>
+        <v>287</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038312</t>
+          <t xml:space="preserve">311082107</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-01</t>
+          <t xml:space="preserve">2024-11-06</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308975</t>
+          <t xml:space="preserve">5309424</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -8240,16 +8240,16 @@
         </is>
       </c>
       <c r="F165">
-        <v>4292</v>
+        <v>2196</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">200049549</t>
+          <t xml:space="preserve">311082106</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-05-26</t>
+          <t xml:space="preserve">2024-11-06</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8281,25 +8281,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304086</t>
+          <t xml:space="preserve">8995636</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F166">
-        <v>1906</v>
+        <v>426</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">200050785</t>
+          <t xml:space="preserve">311082104</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-06-29</t>
+          <t xml:space="preserve">2024-11-06</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8331,25 +8331,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307061</t>
+          <t xml:space="preserve">5312015</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">139</t>
         </is>
       </c>
       <c r="F167">
-        <v>573</v>
+        <v>20718</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057196</t>
+          <t xml:space="preserve">311083529</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-06</t>
+          <t xml:space="preserve">2024-11-14</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8381,25 +8381,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">8135053</t>
+          <t xml:space="preserve">5312015</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="F168">
-        <v>9546</v>
+        <v>927</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057529</t>
+          <t xml:space="preserve">311083529</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-20</t>
+          <t xml:space="preserve">2024-11-14</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172718</t>
+          <t xml:space="preserve">5312115</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -8440,16 +8440,16 @@
         </is>
       </c>
       <c r="F169">
-        <v>1898</v>
+        <v>1048</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057621</t>
+          <t xml:space="preserve">311083539</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-23</t>
+          <t xml:space="preserve">2024-11-14</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8481,25 +8481,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">7938930</t>
+          <t xml:space="preserve">5308584</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F170">
-        <v>638</v>
+        <v>497</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">200060567</t>
+          <t xml:space="preserve">311091392</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-06-29</t>
+          <t xml:space="preserve">2025-01-16</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8531,25 +8531,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2179645</t>
+          <t xml:space="preserve">5312309</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F171">
-        <v>677</v>
+        <v>568</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311052501</t>
+          <t xml:space="preserve">311096313</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-05-06</t>
+          <t xml:space="preserve">2025-02-19</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8581,25 +8581,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312015</t>
+          <t xml:space="preserve">5312309</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F172">
-        <v>927</v>
+        <v>568</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311081839</t>
+          <t xml:space="preserve">311096313</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-05</t>
+          <t xml:space="preserve">2025-02-19</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8631,25 +8631,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174626</t>
+          <t xml:space="preserve">5312309</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F173">
-        <v>287</v>
+        <v>568</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311082107</t>
+          <t xml:space="preserve">311096313</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-06</t>
+          <t xml:space="preserve">2025-02-19</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8681,25 +8681,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5309424</t>
+          <t xml:space="preserve">2177192</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F174">
-        <v>2196</v>
+        <v>268</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311082106</t>
+          <t xml:space="preserve">311098182</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-06</t>
+          <t xml:space="preserve">2025-03-02</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8731,25 +8731,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995636</t>
+          <t xml:space="preserve">2174669</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F175">
-        <v>426</v>
+        <v>401</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311082104</t>
+          <t xml:space="preserve">311101306</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-06</t>
+          <t xml:space="preserve">2025-03-17</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312115</t>
+          <t xml:space="preserve">5303417</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -8790,16 +8790,16 @@
         </is>
       </c>
       <c r="F176">
-        <v>1048</v>
+        <v>482</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311083539</t>
+          <t xml:space="preserve">311109494</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-14</t>
+          <t xml:space="preserve">2025-04-28</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8831,25 +8831,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312309</t>
+          <t xml:space="preserve">5312664, 100884612</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F177">
-        <v>568</v>
+        <v>345</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311096313</t>
+          <t xml:space="preserve">311110647</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-02-19</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8881,25 +8881,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312309</t>
+          <t xml:space="preserve">5303695</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F178">
-        <v>568</v>
+        <v>496</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311096313</t>
+          <t xml:space="preserve">311112925</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-02-19</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8931,25 +8931,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312309</t>
+          <t xml:space="preserve">5303695</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F179">
-        <v>568</v>
+        <v>624</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311096313</t>
+          <t xml:space="preserve">311112925</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-02-19</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8981,25 +8981,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2177192</t>
+          <t xml:space="preserve">5303695</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F180">
-        <v>268</v>
+        <v>667</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311098182</t>
+          <t xml:space="preserve">311112925</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-02</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9031,25 +9031,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174669</t>
+          <t xml:space="preserve">5303695</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F181">
-        <v>401</v>
+        <v>667</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311101306</t>
+          <t xml:space="preserve">311112925</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-17</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303417</t>
+          <t xml:space="preserve">5312565</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -9090,16 +9090,16 @@
         </is>
       </c>
       <c r="F182">
-        <v>482</v>
+        <v>3282</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311109494</t>
+          <t xml:space="preserve">311115034</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-28</t>
+          <t xml:space="preserve">2025-05-26</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9131,25 +9131,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303695</t>
+          <t xml:space="preserve">2170239</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F183">
-        <v>496</v>
+        <v>640</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311112925</t>
+          <t xml:space="preserve">311118198</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-06-10</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9181,25 +9181,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303695</t>
+          <t xml:space="preserve">7175316</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F184">
-        <v>624</v>
+        <v>362</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311112925</t>
+          <t xml:space="preserve">311118205</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-06-10</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9231,25 +9231,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303695</t>
+          <t xml:space="preserve">2209531</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F185">
-        <v>667</v>
+        <v>1432</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311112925</t>
+          <t xml:space="preserve">311124782</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-07-13</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9281,25 +9281,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303695</t>
+          <t xml:space="preserve">2209531</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F186">
-        <v>667</v>
+        <v>979</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311112925</t>
+          <t xml:space="preserve">311124782</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-07-13</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9331,25 +9331,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312565</t>
+          <t xml:space="preserve">719145, 100067704</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F187">
-        <v>3282</v>
+        <v>3529</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311115034</t>
+          <t xml:space="preserve">311137096</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-26</t>
+          <t xml:space="preserve">2025-09-28</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">7175316</t>
+          <t xml:space="preserve">8995769</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -9390,16 +9390,16 @@
         </is>
       </c>
       <c r="F188">
-        <v>362</v>
+        <v>1236</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311118205</t>
+          <t xml:space="preserve">311162791</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-10</t>
+          <t xml:space="preserve">2026-03-07</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9431,35 +9431,35 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209531</t>
+          <t xml:space="preserve">719290, 100013803</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F189">
-        <v>1432</v>
+        <v>276</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311124782</t>
+          <t xml:space="preserve">311241595</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-13</t>
+          <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -9481,35 +9481,35 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209531</t>
+          <t xml:space="preserve">719167, 100093183</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="F190">
-        <v>979</v>
+        <v>2980</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311124782</t>
+          <t xml:space="preserve">311351867</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-13</t>
+          <t xml:space="preserve">2028-12-17</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995769</t>
+          <t xml:space="preserve">100122346</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -9540,26 +9540,26 @@
         </is>
       </c>
       <c r="F191">
-        <v>1236</v>
+        <v>9549</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311162791</t>
+          <t xml:space="preserve">311522399</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-07</t>
+          <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -9581,25 +9581,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">719167, 100093183</t>
+          <t xml:space="preserve">7855029</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F192">
-        <v>2980</v>
+        <v>1530</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311351867</t>
+          <t xml:space="preserve">311552201</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-17</t>
+          <t xml:space="preserve">2031-09-30</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">100122346</t>
+          <t xml:space="preserve">1304635</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -9640,16 +9640,16 @@
         </is>
       </c>
       <c r="F193">
-        <v>9549</v>
+        <v>599</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522399</t>
+          <t xml:space="preserve">311569226</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -9681,25 +9681,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">7855029</t>
+          <t xml:space="preserve">9840711</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F194">
-        <v>1530</v>
+        <v>1459</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311552201</t>
+          <t xml:space="preserve">311570325</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-30</t>
+          <t xml:space="preserve">2032-01-03</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -9731,25 +9731,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">1304635</t>
+          <t xml:space="preserve">9840711</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F195">
-        <v>599</v>
+        <v>355</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569226</t>
+          <t xml:space="preserve">311570327</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-21</t>
+          <t xml:space="preserve">2032-01-03</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">9840711</t>
+          <t xml:space="preserve">5312139</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -9790,16 +9790,16 @@
         </is>
       </c>
       <c r="F196">
-        <v>1459</v>
+        <v>826</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570325</t>
+          <t xml:space="preserve">311595512</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-03</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9831,25 +9831,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">9840711</t>
+          <t xml:space="preserve">7174735</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F197">
-        <v>355</v>
+        <v>435</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570327</t>
+          <t xml:space="preserve">311586207</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-03</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9881,20 +9881,20 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312139</t>
+          <t xml:space="preserve">7174735</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F198">
-        <v>826</v>
+        <v>477</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311595512</t>
+          <t xml:space="preserve">311586207</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -9936,11 +9936,11 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F199">
-        <v>435</v>
+        <v>517</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -9986,11 +9986,11 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F200">
-        <v>477</v>
+        <v>258</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -10031,25 +10031,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">7174735</t>
+          <t xml:space="preserve">5307061</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F201">
-        <v>517</v>
+        <v>322</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586207</t>
+          <t xml:space="preserve">311587049</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-22</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -10081,25 +10081,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">7174735</t>
+          <t xml:space="preserve">2211135</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F202">
-        <v>258</v>
+        <v>469</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586207</t>
+          <t xml:space="preserve">311608657</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-06-17</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -10131,25 +10131,25 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307061</t>
+          <t xml:space="preserve">2211135</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F203">
-        <v>322</v>
+        <v>4564</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587049</t>
+          <t xml:space="preserve">311610029</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-22</t>
+          <t xml:space="preserve">2032-06-23</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -10186,20 +10186,20 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F204">
-        <v>469</v>
+        <v>2127</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311608657</t>
+          <t xml:space="preserve">311610029</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-17</t>
+          <t xml:space="preserve">2032-06-23</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -10236,15 +10236,15 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F205">
-        <v>4564</v>
+        <v>1898</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610029</t>
+          <t xml:space="preserve">311610041</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -10286,11 +10286,11 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F206">
-        <v>2127</v>
+        <v>847</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -10331,25 +10331,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211135</t>
+          <t xml:space="preserve">5308417</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F207">
-        <v>1898</v>
+        <v>1620</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610041</t>
+          <t xml:space="preserve">311626283</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-23</t>
+          <t xml:space="preserve">2032-09-08</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -10381,25 +10381,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211135</t>
+          <t xml:space="preserve">2170541</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F208">
-        <v>847</v>
+        <v>1257</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610029</t>
+          <t xml:space="preserve">311633102</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-23</t>
+          <t xml:space="preserve">2032-10-04</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -10431,25 +10431,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308417</t>
+          <t xml:space="preserve">2202050</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F209">
-        <v>1620</v>
+        <v>438</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626283</t>
+          <t xml:space="preserve">311633105</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-08</t>
+          <t xml:space="preserve">2032-10-04</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2170541</t>
+          <t xml:space="preserve">8016122</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -10490,16 +10490,16 @@
         </is>
       </c>
       <c r="F210">
-        <v>1257</v>
+        <v>2104</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311633102</t>
+          <t xml:space="preserve">311645050</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-04</t>
+          <t xml:space="preserve">2032-11-08</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -10531,25 +10531,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2202050</t>
+          <t xml:space="preserve">8016122</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F211">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311633105</t>
+          <t xml:space="preserve">311645050</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-04</t>
+          <t xml:space="preserve">2032-11-08</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">8016122</t>
+          <t xml:space="preserve">8934798</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -10590,16 +10590,16 @@
         </is>
       </c>
       <c r="F212">
-        <v>2104</v>
+        <v>1378</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645050</t>
+          <t xml:space="preserve">311642567</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-08</t>
+          <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -10631,25 +10631,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">8016122</t>
+          <t xml:space="preserve">2167605</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F213">
-        <v>434</v>
+        <v>979</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645050</t>
+          <t xml:space="preserve">311643576</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-08</t>
+          <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -10686,15 +10686,15 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F214">
-        <v>979</v>
+        <v>4101</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643576</t>
+          <t xml:space="preserve">311643577</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -10731,25 +10731,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167605</t>
+          <t xml:space="preserve">2172270</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F215">
-        <v>4101</v>
+        <v>3519</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643577</t>
+          <t xml:space="preserve">311644570</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2032-11-23</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172270</t>
+          <t xml:space="preserve">8907547</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -10790,16 +10790,16 @@
         </is>
       </c>
       <c r="F216">
-        <v>3519</v>
+        <v>897</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644570</t>
+          <t xml:space="preserve">311644810</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-23</t>
+          <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -10836,11 +10836,11 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F217">
-        <v>897</v>
+        <v>398</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -10886,11 +10886,11 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F218">
-        <v>398</v>
+        <v>1311</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -10936,11 +10936,11 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F219">
-        <v>1311</v>
+        <v>924</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -10986,11 +10986,11 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F220">
-        <v>924</v>
+        <v>487</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -11036,11 +11036,11 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F221">
-        <v>487</v>
+        <v>256</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F222">
@@ -11136,11 +11136,11 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F223">
-        <v>256</v>
+        <v>897</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -11186,11 +11186,11 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F224">
-        <v>897</v>
+        <v>983</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -11236,11 +11236,11 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F225">
-        <v>983</v>
+        <v>552</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -11286,11 +11286,11 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F226">
-        <v>552</v>
+        <v>897</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F227">
@@ -11386,11 +11386,11 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F228">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -11436,11 +11436,11 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F229">
-        <v>898</v>
+        <v>280</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -11486,11 +11486,11 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F230">
-        <v>280</v>
+        <v>900</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -11536,11 +11536,11 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F231">
-        <v>900</v>
+        <v>789</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
@@ -11581,25 +11581,25 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">8907547</t>
+          <t xml:space="preserve">2173007</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F232">
-        <v>789</v>
+        <v>7796</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644810</t>
+          <t xml:space="preserve">311645058</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-24</t>
+          <t xml:space="preserve">2032-11-25</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2173007</t>
+          <t xml:space="preserve">2180519</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -11640,11 +11640,11 @@
         </is>
       </c>
       <c r="F233">
-        <v>7796</v>
+        <v>1448</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645058</t>
+          <t xml:space="preserve">311644999</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -11686,11 +11686,11 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F234">
-        <v>1448</v>
+        <v>413</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
@@ -11731,25 +11731,25 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2180519</t>
+          <t xml:space="preserve">5306821</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F235">
-        <v>413</v>
+        <v>12072</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644999</t>
+          <t xml:space="preserve">311645727</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-25</t>
+          <t xml:space="preserve">2032-11-29</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -11786,11 +11786,11 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F236">
-        <v>12072</v>
+        <v>5829</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -11831,25 +11831,25 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306821</t>
+          <t xml:space="preserve">2213437</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F237">
-        <v>5829</v>
+        <v>2744</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645727</t>
+          <t xml:space="preserve">311646168</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-29</t>
+          <t xml:space="preserve">2032-11-30</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -11886,15 +11886,15 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F238">
-        <v>2744</v>
+        <v>1287</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646168</t>
+          <t xml:space="preserve">311646167</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -11931,25 +11931,25 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213437</t>
+          <t xml:space="preserve">2209330</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F239">
-        <v>1287</v>
+        <v>5956</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646167</t>
+          <t xml:space="preserve">311646682</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-30</t>
+          <t xml:space="preserve">2032-12-02</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -11986,15 +11986,15 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F240">
-        <v>5956</v>
+        <v>447</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646682</t>
+          <t xml:space="preserve">311646683</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -12031,25 +12031,25 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209330</t>
+          <t xml:space="preserve">9700889</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F241">
-        <v>447</v>
+        <v>2442</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646683</t>
+          <t xml:space="preserve">311647649</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-02</t>
+          <t xml:space="preserve">2032-12-07</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -12086,20 +12086,20 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F242">
-        <v>2442</v>
+        <v>1517</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647649</t>
+          <t xml:space="preserve">311647742</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-07</t>
+          <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -12136,11 +12136,11 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F243">
-        <v>1517</v>
+        <v>1514</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
@@ -12186,11 +12186,11 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F244">
-        <v>1514</v>
+        <v>1500</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
@@ -12236,11 +12236,11 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F245">
-        <v>1500</v>
+        <v>1577</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
@@ -12286,11 +12286,11 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F246">
-        <v>1577</v>
+        <v>1500</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
@@ -12331,25 +12331,25 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">9700889</t>
+          <t xml:space="preserve">7713101</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F247">
-        <v>1500</v>
+        <v>11744</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647742</t>
+          <t xml:space="preserve">311649946</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-08</t>
+          <t xml:space="preserve">2032-12-17</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -12386,20 +12386,20 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F248">
-        <v>11744</v>
+        <v>1185</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649946</t>
+          <t xml:space="preserve">311649970</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-17</t>
+          <t xml:space="preserve">2032-12-18</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -12431,25 +12431,25 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">7713101</t>
+          <t xml:space="preserve">2177192</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F249">
-        <v>1185</v>
+        <v>1786</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649970</t>
+          <t xml:space="preserve">311652564</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-18</t>
+          <t xml:space="preserve">2033-01-05</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -12481,25 +12481,25 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">258624, 258625</t>
+          <t xml:space="preserve">2177192</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F250">
-        <v>4232</v>
+        <v>1585</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650857</t>
+          <t xml:space="preserve">311652563</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-21</t>
+          <t xml:space="preserve">2033-01-05</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -12536,15 +12536,15 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F251">
-        <v>1786</v>
+        <v>610</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652564</t>
+          <t xml:space="preserve">311652565</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -12586,15 +12586,15 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F252">
-        <v>1585</v>
+        <v>2239</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652563</t>
+          <t xml:space="preserve">311652567</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -12631,25 +12631,25 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2177192</t>
+          <t xml:space="preserve">2217238</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F253">
-        <v>610</v>
+        <v>8368</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652565</t>
+          <t xml:space="preserve">311652748</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-05</t>
+          <t xml:space="preserve">2033-01-06</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -12681,25 +12681,25 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2177192</t>
+          <t xml:space="preserve">9840711</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F254">
-        <v>2239</v>
+        <v>1815</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652567</t>
+          <t xml:space="preserve">311652906</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-05</t>
+          <t xml:space="preserve">2033-01-09</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -12731,25 +12731,25 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217238</t>
+          <t xml:space="preserve">9840711</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F255">
-        <v>8368</v>
+        <v>2850</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652748</t>
+          <t xml:space="preserve">311652906</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-06</t>
+          <t xml:space="preserve">2033-01-09</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -12786,11 +12786,11 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F256">
-        <v>1815</v>
+        <v>1908</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
@@ -12831,25 +12831,25 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">9840711</t>
+          <t xml:space="preserve">5304953</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F257">
-        <v>2850</v>
+        <v>6173</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652906</t>
+          <t xml:space="preserve">311656342</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-09</t>
+          <t xml:space="preserve">2033-01-20</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -12881,25 +12881,25 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">9840711</t>
+          <t xml:space="preserve">5311321</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F258">
-        <v>1908</v>
+        <v>9899</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652906</t>
+          <t xml:space="preserve">311655694</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-09</t>
+          <t xml:space="preserve">2033-01-23</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304953</t>
+          <t xml:space="preserve">5306248</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -12940,16 +12940,16 @@
         </is>
       </c>
       <c r="F259">
-        <v>6173</v>
+        <v>8569</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656342</t>
+          <t xml:space="preserve">311656548</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-20</t>
+          <t xml:space="preserve">2033-01-27</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -12981,25 +12981,25 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">5311321</t>
+          <t xml:space="preserve">8207354</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F260">
-        <v>9899</v>
+        <v>9084</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655694</t>
+          <t xml:space="preserve">311656779</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-23</t>
+          <t xml:space="preserve">2033-01-30</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -13036,20 +13036,20 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F261">
-        <v>9084</v>
+        <v>440</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655558</t>
+          <t xml:space="preserve">311656779</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-23</t>
+          <t xml:space="preserve">2033-01-30</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -13081,25 +13081,25 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306248</t>
+          <t xml:space="preserve">8207354</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F262">
-        <v>8569</v>
+        <v>5709</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656548</t>
+          <t xml:space="preserve">311657131</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-27</t>
+          <t xml:space="preserve">2033-01-31</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -13131,25 +13131,25 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">8207354</t>
+          <t xml:space="preserve">5303415</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F263">
-        <v>440</v>
+        <v>858</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656782</t>
+          <t xml:space="preserve">311657449</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-30</t>
+          <t xml:space="preserve">2033-02-01</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -13181,25 +13181,25 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">8207354</t>
+          <t xml:space="preserve">5303415</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F264">
-        <v>5709</v>
+        <v>433</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657131</t>
+          <t xml:space="preserve">311657448</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-31</t>
+          <t xml:space="preserve">2033-02-01</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -13236,15 +13236,15 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F265">
-        <v>858</v>
+        <v>608</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657449</t>
+          <t xml:space="preserve">311657447</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -13281,25 +13281,25 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303415</t>
+          <t xml:space="preserve">8995768</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F266">
-        <v>433</v>
+        <v>6187</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657448</t>
+          <t xml:space="preserve">311659172</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-01</t>
+          <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -13331,25 +13331,25 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303415</t>
+          <t xml:space="preserve">8995768</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F267">
-        <v>608</v>
+        <v>378</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657447</t>
+          <t xml:space="preserve">311659172</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-01</t>
+          <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995768</t>
+          <t xml:space="preserve">8207354</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -13390,16 +13390,16 @@
         </is>
       </c>
       <c r="F268">
-        <v>6187</v>
+        <v>9651</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659172</t>
+          <t xml:space="preserve">311666198</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-09</t>
+          <t xml:space="preserve">2033-02-14</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -13431,25 +13431,25 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995768</t>
+          <t xml:space="preserve">2177368</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F269">
-        <v>378</v>
+        <v>3340</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659172</t>
+          <t xml:space="preserve">311664732</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-09</t>
+          <t xml:space="preserve">2033-03-07</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -13481,25 +13481,25 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">8207354</t>
+          <t xml:space="preserve">2177368</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F270">
-        <v>9651</v>
+        <v>916</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666198</t>
+          <t xml:space="preserve">311664732</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-14</t>
+          <t xml:space="preserve">2033-03-07</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -13536,11 +13536,11 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F271">
-        <v>3340</v>
+        <v>900</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
@@ -13586,11 +13586,11 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F272">
-        <v>916</v>
+        <v>711</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -13636,11 +13636,11 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F273">
-        <v>900</v>
+        <v>1816</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -13681,25 +13681,25 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2177368</t>
+          <t xml:space="preserve">8995659</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F274">
-        <v>711</v>
+        <v>817</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664732</t>
+          <t xml:space="preserve">311665647</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-07</t>
+          <t xml:space="preserve">2033-03-10</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -13731,25 +13731,25 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2177368</t>
+          <t xml:space="preserve">8995659</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F275">
-        <v>1816</v>
+        <v>433</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664732</t>
+          <t xml:space="preserve">311665669</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-07</t>
+          <t xml:space="preserve">2033-03-10</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -13786,15 +13786,15 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F276">
-        <v>817</v>
+        <v>1552</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665647</t>
+          <t xml:space="preserve">311665669</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -13836,20 +13836,20 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F277">
-        <v>433</v>
+        <v>12308</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665669</t>
+          <t xml:space="preserve">311666274</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-10</t>
+          <t xml:space="preserve">2033-03-14</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -13881,25 +13881,25 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995659</t>
+          <t xml:space="preserve">2180546</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F278">
-        <v>1552</v>
+        <v>2200</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665669</t>
+          <t xml:space="preserve">311666541</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-10</t>
+          <t xml:space="preserve">2033-03-15</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -13931,7 +13931,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995659</t>
+          <t xml:space="preserve">5312782</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -13940,16 +13940,16 @@
         </is>
       </c>
       <c r="F279">
-        <v>12308</v>
+        <v>3137</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666274</t>
+          <t xml:space="preserve">311670004</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-14</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -13981,25 +13981,25 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2180546</t>
+          <t xml:space="preserve">5312782</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F280">
-        <v>2200</v>
+        <v>778</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666541</t>
+          <t xml:space="preserve">311670004</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-15</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -14031,25 +14031,25 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2173759</t>
+          <t xml:space="preserve">5312782</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F281">
-        <v>12044</v>
+        <v>6340</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667669</t>
+          <t xml:space="preserve">311670004</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-20</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -14081,25 +14081,25 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2173759</t>
+          <t xml:space="preserve">5312782</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F282">
-        <v>826</v>
+        <v>2165</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667621</t>
+          <t xml:space="preserve">311670004</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-20</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -14136,20 +14136,20 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F283">
-        <v>494</v>
+        <v>12044</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667669</t>
+          <t xml:space="preserve">311670514</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-20</t>
+          <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -14181,25 +14181,25 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312782</t>
+          <t xml:space="preserve">2173759</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F284">
-        <v>3137</v>
+        <v>826</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670004</t>
+          <t xml:space="preserve">311670514</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -14231,25 +14231,25 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312782</t>
+          <t xml:space="preserve">2173759</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F285">
-        <v>778</v>
+        <v>494</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670004</t>
+          <t xml:space="preserve">311670514</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -14281,25 +14281,25 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312782</t>
+          <t xml:space="preserve">2209127</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F286">
-        <v>6340</v>
+        <v>2177</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670004</t>
+          <t xml:space="preserve">311670922</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-03-31</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -14331,25 +14331,25 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312782</t>
+          <t xml:space="preserve">2209127</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F287">
-        <v>2165</v>
+        <v>3318</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670004</t>
+          <t xml:space="preserve">311670922</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-03-31</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -14386,15 +14386,15 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F288">
-        <v>2177</v>
+        <v>2100</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670922</t>
+          <t xml:space="preserve">311670925</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -14436,11 +14436,11 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F289">
-        <v>3318</v>
+        <v>766</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
@@ -14481,25 +14481,25 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209127</t>
+          <t xml:space="preserve">100513814</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">109</t>
         </is>
       </c>
       <c r="F290">
-        <v>2100</v>
+        <v>1000</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670926</t>
+          <t xml:space="preserve">311673245</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-31</t>
+          <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -14531,25 +14531,25 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209127</t>
+          <t xml:space="preserve">100513814</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="F291">
-        <v>766</v>
+        <v>1077</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670922</t>
+          <t xml:space="preserve">311675950</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-31</t>
+          <t xml:space="preserve">2033-04-24</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -14586,20 +14586,20 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">109</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F292">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673245</t>
+          <t xml:space="preserve">311675948</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-13</t>
+          <t xml:space="preserve">2033-04-24</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -14631,25 +14631,25 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513814</t>
+          <t xml:space="preserve">8995869</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F293">
-        <v>1077</v>
+        <v>10347</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t xml:space="preserve">311675950</t>
+          <t xml:space="preserve">311676003</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-24</t>
+          <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -14681,25 +14681,25 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513814</t>
+          <t xml:space="preserve">8995869</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F294">
-        <v>997</v>
+        <v>6038</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t xml:space="preserve">311675948</t>
+          <t xml:space="preserve">311676003</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-24</t>
+          <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -14736,15 +14736,15 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F295">
-        <v>10347</v>
+        <v>643</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">311676003</t>
+          <t xml:space="preserve">311676217</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995869</t>
+          <t xml:space="preserve">2217238</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -14790,16 +14790,16 @@
         </is>
       </c>
       <c r="F296">
-        <v>6038</v>
+        <v>585</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t xml:space="preserve">311676003</t>
+          <t xml:space="preserve">311679099</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-25</t>
+          <t xml:space="preserve">2033-05-08</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -14831,25 +14831,25 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995869</t>
+          <t xml:space="preserve">9306000</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F297">
-        <v>643</v>
+        <v>6671</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311676217</t>
+          <t xml:space="preserve">311683472</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-25</t>
+          <t xml:space="preserve">2033-05-26</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217238</t>
+          <t xml:space="preserve">9306000</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -14890,16 +14890,16 @@
         </is>
       </c>
       <c r="F298">
-        <v>585</v>
+        <v>3994</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679099</t>
+          <t xml:space="preserve">311683472</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-08</t>
+          <t xml:space="preserve">2033-05-26</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">9306000</t>
+          <t xml:space="preserve">9306001</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -14940,16 +14940,16 @@
         </is>
       </c>
       <c r="F299">
-        <v>6671</v>
+        <v>630</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683094</t>
+          <t xml:space="preserve">311683580</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-25</t>
+          <t xml:space="preserve">2033-05-26</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">9306001</t>
+          <t xml:space="preserve">2174448</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -14990,16 +14990,16 @@
         </is>
       </c>
       <c r="F300">
-        <v>630</v>
+        <v>1216</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683580</t>
+          <t xml:space="preserve">311725437</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-26</t>
+          <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -15036,11 +15036,11 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F301">
-        <v>1216</v>
+        <v>1537</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
@@ -15086,11 +15086,11 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F302">
-        <v>1537</v>
+        <v>962</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
@@ -15136,11 +15136,11 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F303">
-        <v>962</v>
+        <v>3144</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
@@ -15186,15 +15186,15 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F304">
-        <v>3144</v>
+        <v>2011</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725437</t>
+          <t xml:space="preserve">311725438</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -15236,15 +15236,15 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F305">
-        <v>2011</v>
+        <v>929</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725438</t>
+          <t xml:space="preserve">311725437</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -15286,11 +15286,11 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F306">
-        <v>929</v>
+        <v>553</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
@@ -15336,11 +15336,11 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F307">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
@@ -15386,15 +15386,15 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F308">
-        <v>548</v>
+        <v>599</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725437</t>
+          <t xml:space="preserve">311725441</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -15436,15 +15436,15 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F309">
-        <v>599</v>
+        <v>715</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725441</t>
+          <t xml:space="preserve">311725437</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -15481,25 +15481,25 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174448</t>
+          <t xml:space="preserve">2172114</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F310">
-        <v>715</v>
+        <v>595</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725437</t>
+          <t xml:space="preserve">311743780</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-29</t>
+          <t xml:space="preserve">2034-03-07</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -15531,25 +15531,25 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172114</t>
+          <t xml:space="preserve">8934798</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F311">
-        <v>595</v>
+        <v>686</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743780</t>
+          <t xml:space="preserve">311787742</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-07</t>
+          <t xml:space="preserve">2034-09-26</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -15586,11 +15586,11 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F312">
-        <v>686</v>
+        <v>452</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
@@ -15636,15 +15636,15 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F313">
-        <v>452</v>
+        <v>479</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787742</t>
+          <t xml:space="preserve">311787741</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -15686,15 +15686,15 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F314">
-        <v>479</v>
+        <v>310</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787741</t>
+          <t xml:space="preserve">311787745</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -15731,25 +15731,25 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">8934798</t>
+          <t xml:space="preserve">2209127</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F315">
-        <v>310</v>
+        <v>470</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t xml:space="preserve">311787745</t>
+          <t xml:space="preserve">311793891</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-26</t>
+          <t xml:space="preserve">2034-10-28</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -15781,25 +15781,25 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209127</t>
+          <t xml:space="preserve">2171290</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F316">
-        <v>470</v>
+        <v>379</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">311793891</t>
+          <t xml:space="preserve">311827298</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-28</t>
+          <t xml:space="preserve">2035-04-25</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2171290</t>
+          <t xml:space="preserve">2170150</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -15840,16 +15840,16 @@
         </is>
       </c>
       <c r="F317">
-        <v>379</v>
+        <v>1122</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827298</t>
+          <t xml:space="preserve">311827519</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-25</t>
+          <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -15881,7 +15881,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2170150</t>
+          <t xml:space="preserve">2179764</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -15890,16 +15890,16 @@
         </is>
       </c>
       <c r="F318">
-        <v>1122</v>
+        <v>6510</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827519</t>
+          <t xml:space="preserve">311836213</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-28</t>
+          <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -15931,25 +15931,25 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2179764</t>
+          <t xml:space="preserve">2174627</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F319">
-        <v>6510</v>
+        <v>410</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311836213</t>
+          <t xml:space="preserve">311842230</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-04</t>
+          <t xml:space="preserve">2035-07-02</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -15981,25 +15981,25 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174627</t>
+          <t xml:space="preserve">100072983</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F320">
-        <v>410</v>
+        <v>280</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842230</t>
+          <t xml:space="preserve">311846096</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-02</t>
+          <t xml:space="preserve">2035-07-24</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">

--- a/public/exports/29189404.xlsx
+++ b/public/exports/29189404.xlsx
@@ -91,26 +91,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spraglehøjvej 3</t>
+          <t xml:space="preserve">Absalonsgade 13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100043785</t>
+          <t xml:space="preserve">8173183</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H2">
-        <v>283</v>
+        <v>1323</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllehusvej 13</t>
+          <t xml:space="preserve">Absalonsgade 3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -161,16 +161,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100069011</t>
+          <t xml:space="preserve">8173183</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H3">
-        <v>5391</v>
+        <v>1260</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,7 +211,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftebakken 9</t>
+          <t xml:space="preserve">Absalonsgade 7B</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -221,16 +221,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100078592</t>
+          <t xml:space="preserve">8173183</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H4">
-        <v>323</v>
+        <v>1867</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftebakken 10</t>
+          <t xml:space="preserve">Bagtæppet 8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,16 +281,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">100078592</t>
+          <t xml:space="preserve">5308146</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H5">
-        <v>288</v>
+        <v>350</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftebakken 11</t>
+          <t xml:space="preserve">Bakkesvinget 67</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">100078592</t>
+          <t xml:space="preserve">271130, 271131</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H6">
-        <v>473</v>
+        <v>13568</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,7 +391,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådmandshaven 4B</t>
+          <t xml:space="preserve">Basgangen 16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -401,16 +401,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">100096939</t>
+          <t xml:space="preserve">719167, 100093183</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H7">
-        <v>660</v>
+        <v>1068</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,7 +451,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 106G</t>
+          <t xml:space="preserve">Basgangen 18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -461,16 +461,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">100101318</t>
+          <t xml:space="preserve">719167, 100093183</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H8">
-        <v>330</v>
+        <v>1068</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,26 +511,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegården 7</t>
+          <t xml:space="preserve">Baunegårdsvej 85</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">100197946</t>
+          <t xml:space="preserve">2177368</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H9">
-        <v>392</v>
+        <v>987</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bindesbøll Alle 6</t>
+          <t xml:space="preserve">Bindesbøll Alle 10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,16 +581,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513809</t>
+          <t xml:space="preserve">100513810</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H10">
-        <v>2037</v>
+        <v>2429</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bindesbøll Alle 10</t>
+          <t xml:space="preserve">Bindesbøll Alle 32</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,16 +641,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513810</t>
+          <t xml:space="preserve">100513820</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">128</t>
         </is>
       </c>
       <c r="H11">
-        <v>2429</v>
+        <v>463</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parcelgårdsvej 2</t>
+          <t xml:space="preserve">Bindesbøll Alle 35</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,16 +701,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513811</t>
+          <t xml:space="preserve">100513822</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">118</t>
         </is>
       </c>
       <c r="H12">
-        <v>252</v>
+        <v>637</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrupvænge 2</t>
+          <t xml:space="preserve">Bindesbøll Alle 6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,16 +761,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513812</t>
+          <t xml:space="preserve">100513809</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">52</t>
         </is>
       </c>
       <c r="H13">
-        <v>1728</v>
+        <v>2037</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Alle 7</t>
+          <t xml:space="preserve">Bistrupvænge 14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -821,16 +821,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513815</t>
+          <t xml:space="preserve">100513819</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">117</t>
         </is>
       </c>
       <c r="H14">
-        <v>475</v>
+        <v>4873</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kurhusvænge 6</t>
+          <t xml:space="preserve">Bistrupvænge 2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -881,16 +881,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513816</t>
+          <t xml:space="preserve">100513812</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="H15">
-        <v>1204</v>
+        <v>1728</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrupvænge 14</t>
+          <t xml:space="preserve">Bondetinget 22</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -941,16 +941,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513819</t>
+          <t xml:space="preserve">5304129</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">117</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H16">
-        <v>4873</v>
+        <v>394</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,26 +991,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bindesbøll Alle 32</t>
+          <t xml:space="preserve">Bygaden 19</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513820</t>
+          <t xml:space="preserve">2176798</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">128</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H17">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krathusvænge 8</t>
+          <t xml:space="preserve">Darupvej 52</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,16 +1061,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513821</t>
+          <t xml:space="preserve">719219, 5307564</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H18">
-        <v>566</v>
+        <v>3050</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bindesbøll Alle 35</t>
+          <t xml:space="preserve">Dronning Margrethes Vej 28</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1121,16 +1121,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513822</t>
+          <t xml:space="preserve">5304873</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">118</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H19">
-        <v>637</v>
+        <v>1000</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Alle 5</t>
+          <t xml:space="preserve">Dyssevej 37</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1181,16 +1181,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">100513824</t>
+          <t xml:space="preserve">2167800</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H20">
-        <v>280</v>
+        <v>337</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Hans Gade 40</t>
+          <t xml:space="preserve">Eriksvej 40A</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352513</t>
+          <t xml:space="preserve">5308263</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H21">
-        <v>525</v>
+        <v>661</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedegade 21</t>
+          <t xml:space="preserve">Eriksvej 50B</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352516</t>
+          <t xml:space="preserve">719268, 5308429</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="H22">
-        <v>590</v>
+        <v>266</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågerupvej 24</t>
+          <t xml:space="preserve">Frederiksborgvej 21</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167528</t>
+          <t xml:space="preserve">5304824</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="H23">
-        <v>444</v>
+        <v>254</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyssevej 37</t>
+          <t xml:space="preserve">Gulddyssevej 70</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1421,16 +1421,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167800</t>
+          <t xml:space="preserve">8919779</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H24">
-        <v>337</v>
+        <v>472</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sognevej 4B</t>
+          <t xml:space="preserve">Haraldsborgvej 78</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2171273</t>
+          <t xml:space="preserve">5305533</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="H25">
-        <v>300</v>
+        <v>912</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herregårdsvej 46</t>
+          <t xml:space="preserve">Havnevej 47B</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1541,16 +1541,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172704</t>
+          <t xml:space="preserve">719175, 5305606</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H26">
-        <v>469</v>
+        <v>1440</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herregårdsvej 48</t>
+          <t xml:space="preserve">Herregårdsvej 46</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1601,16 +1601,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172718</t>
+          <t xml:space="preserve">2172704</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H27">
-        <v>1318</v>
+        <v>469</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store Valbyvej 150</t>
+          <t xml:space="preserve">Herregårdsvej 48</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,16 +1661,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174609</t>
+          <t xml:space="preserve">2172718</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H28">
-        <v>313</v>
+        <v>1318</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1711,17 +1711,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindbjergvej 4</t>
+          <t xml:space="preserve">Herregårdsvej 61</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2175641</t>
+          <t xml:space="preserve">9888274</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="H29">
-        <v>397</v>
+        <v>1776</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1771,26 +1771,26 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 10</t>
+          <t xml:space="preserve">Herregårdsvej 61</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2175645</t>
+          <t xml:space="preserve">9888274</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H30">
-        <v>565</v>
+        <v>788</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1831,26 +1831,26 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 19</t>
+          <t xml:space="preserve">Himmelev Bygade 15</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2176798</t>
+          <t xml:space="preserve">9883833</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H31">
-        <v>445</v>
+        <v>378</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1891,26 +1891,26 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunegårdsvej 85</t>
+          <t xml:space="preserve">Himmelev Bygade 22A</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2177368</t>
+          <t xml:space="preserve">8995636</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H32">
-        <v>987</v>
+        <v>405</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stærkendevej 13</t>
+          <t xml:space="preserve">Indfaldet 4</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1961,16 +1961,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209116</t>
+          <t xml:space="preserve">5308164</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">74</t>
         </is>
       </c>
       <c r="H33">
-        <v>342</v>
+        <v>5006</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2011,26 +2011,26 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 21</t>
+          <t xml:space="preserve">Kildegården 1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213458</t>
+          <t xml:space="preserve">5309842</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H34">
-        <v>295</v>
+        <v>4510</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2071,26 +2071,26 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyvej 42</t>
+          <t xml:space="preserve">Kildegården 10</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213556</t>
+          <t xml:space="preserve">5308734</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H35">
-        <v>335</v>
+        <v>261</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2131,17 +2131,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyvej 52</t>
+          <t xml:space="preserve">Kildegården 13</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213556</t>
+          <t xml:space="preserve">5308734</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="H36">
-        <v>469</v>
+        <v>291</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2191,26 +2191,26 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tofthøjvej 11</t>
+          <t xml:space="preserve">Kildegården 2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217131</t>
+          <t xml:space="preserve">5308734</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H37">
-        <v>866</v>
+        <v>307</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2251,26 +2251,26 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 32</t>
+          <t xml:space="preserve">Kildegården 5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217717</t>
+          <t xml:space="preserve">5308734</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H38">
-        <v>586</v>
+        <v>1747</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2311,26 +2311,26 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindevej 34</t>
+          <t xml:space="preserve">Kildegården 6</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217717</t>
+          <t xml:space="preserve">5308734</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H39">
-        <v>2746</v>
+        <v>3208</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllehusvej 118</t>
+          <t xml:space="preserve">Kildegården 7</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2381,16 +2381,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">258624, 258625</t>
+          <t xml:space="preserve">100197946</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H40">
-        <v>4232</v>
+        <v>392</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkesvinget 67</t>
+          <t xml:space="preserve">Kildegården 8</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2441,16 +2441,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">271130, 271131</t>
+          <t xml:space="preserve">5308734</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H41">
-        <v>13568</v>
+        <v>291</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Læderstræde 6</t>
+          <t xml:space="preserve">Kildegården 9</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,16 +2501,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303635</t>
+          <t xml:space="preserve">5308734</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H42">
-        <v>632</v>
+        <v>883</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stændertorvet 1B</t>
+          <t xml:space="preserve">Krathusvænge 8</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2561,16 +2561,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304088</t>
+          <t xml:space="preserve">100513821</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="H43">
-        <v>852</v>
+        <v>566</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bondetinget 22</t>
+          <t xml:space="preserve">Kurhusvænge 6</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304129</t>
+          <t xml:space="preserve">100513816</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="H44">
-        <v>394</v>
+        <v>1204</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksborgvej 21</t>
+          <t xml:space="preserve">Københavnsvej 106G</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2681,16 +2681,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304824</t>
+          <t xml:space="preserve">100101318</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H45">
-        <v>254</v>
+        <v>330</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Margrethes Vej 28</t>
+          <t xml:space="preserve">Køgevej 5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304873</t>
+          <t xml:space="preserve">8245209</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="H46">
-        <v>1000</v>
+        <v>764</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2791,17 +2791,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stændertorvet 19</t>
+          <t xml:space="preserve">Lindbjergvej 4</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5305072</t>
+          <t xml:space="preserve">2175641</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="H47">
-        <v>322</v>
+        <v>397</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2851,17 +2851,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Haraldsborgvej 78</t>
+          <t xml:space="preserve">Lindevej 32</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5305533</t>
+          <t xml:space="preserve">2217717</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2870,7 +2870,7 @@
         </is>
       </c>
       <c r="H48">
-        <v>912</v>
+        <v>586</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2911,26 +2911,26 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Penselstrøget 62</t>
+          <t xml:space="preserve">Lindevej 34</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308146</t>
+          <t xml:space="preserve">2217717</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H49">
-        <v>1740</v>
+        <v>2746</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagtæppet 8</t>
+          <t xml:space="preserve">Læderstræde 6</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2981,16 +2981,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308146</t>
+          <t xml:space="preserve">5303635</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H50">
-        <v>350</v>
+        <v>632</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rabalderstræde 29</t>
+          <t xml:space="preserve">Margrethehåbsvej 66</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3041,16 +3041,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308164</t>
+          <t xml:space="preserve">5313168</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">73</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H51">
-        <v>462</v>
+        <v>819</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indfaldet 4</t>
+          <t xml:space="preserve">Margrethehåbsvej 68</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3101,16 +3101,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308164</t>
+          <t xml:space="preserve">7969204</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">74</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H52">
-        <v>5006</v>
+        <v>1000</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eriksvej 40A</t>
+          <t xml:space="preserve">Møllehusvej 13</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3161,16 +3161,16 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308263</t>
+          <t xml:space="preserve">100069011</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H53">
-        <v>661</v>
+        <v>5391</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3211,17 +3211,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegården 6</t>
+          <t xml:space="preserve">Møllevej 10</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308734</t>
+          <t xml:space="preserve">2175645</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="H54">
-        <v>3208</v>
+        <v>565</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3271,26 +3271,26 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegården 8</t>
+          <t xml:space="preserve">Nyvej 42</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308734</t>
+          <t xml:space="preserve">2213556</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H55">
-        <v>291</v>
+        <v>335</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3331,26 +3331,26 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegården 5</t>
+          <t xml:space="preserve">Nyvej 52</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308734</t>
+          <t xml:space="preserve">2213556</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H56">
-        <v>1747</v>
+        <v>469</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegården 13</t>
+          <t xml:space="preserve">Parcelgårdsvej 2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3401,16 +3401,16 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308734</t>
+          <t xml:space="preserve">100513811</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="H57">
-        <v>291</v>
+        <v>252</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegården 2</t>
+          <t xml:space="preserve">Peblingevej 2B</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3461,16 +3461,16 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308734</t>
+          <t xml:space="preserve">8908094</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H58">
-        <v>307</v>
+        <v>692</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegården 10</t>
+          <t xml:space="preserve">Penselstrøget 62</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3521,16 +3521,16 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308734</t>
+          <t xml:space="preserve">5308146</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H59">
-        <v>261</v>
+        <v>1740</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3571,26 +3571,26 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegården 9</t>
+          <t xml:space="preserve">Planetvej 30B</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308734</t>
+          <t xml:space="preserve">719295, 8907547</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="H60">
-        <v>883</v>
+        <v>294</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegården 1</t>
+          <t xml:space="preserve">Rabalderstræde 10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3641,16 +3641,16 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5309842</t>
+          <t xml:space="preserve">8377662</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H61">
-        <v>4510</v>
+        <v>553</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethehåbsvej 66</t>
+          <t xml:space="preserve">Rabalderstræde 29</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3701,16 +3701,16 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5313168</t>
+          <t xml:space="preserve">5308164</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">73</t>
         </is>
       </c>
       <c r="H62">
-        <v>819</v>
+        <v>462</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3811,26 +3811,26 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Basgangen 16</t>
+          <t xml:space="preserve">Ramsømaglevej 21</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">719167, 100093183</t>
+          <t xml:space="preserve">2213458</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H64">
-        <v>1068</v>
+        <v>295</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Basgangen 18</t>
+          <t xml:space="preserve">Rådmandshaven 4B</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3881,16 +3881,16 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">719167, 100093183</t>
+          <t xml:space="preserve">100096939</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H65">
-        <v>1068</v>
+        <v>660</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 47B</t>
+          <t xml:space="preserve">Sandvejen 28</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3941,16 +3941,16 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">719175, 5305606</t>
+          <t xml:space="preserve">719194, 2209303</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H66">
-        <v>1440</v>
+        <v>348</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandvejen 28</t>
+          <t xml:space="preserve">Sankt Clara Vej 41</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4001,16 +4001,16 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">719194, 2209303</t>
+          <t xml:space="preserve">719209, 8934795</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="H67">
-        <v>348</v>
+        <v>1980</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindeboder 20</t>
+          <t xml:space="preserve">Sankt Hans Gade 40</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">719209, 8934795</t>
+          <t xml:space="preserve">1352513</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="H68">
-        <v>400</v>
+        <v>525</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -4111,26 +4111,26 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Clara Vej 41</t>
+          <t xml:space="preserve">Skovbrynet 4B</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">719209, 8934795</t>
+          <t xml:space="preserve">719337, 9604964</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H69">
-        <v>1980</v>
+        <v>662</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -4171,17 +4171,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindeboder 20</t>
+          <t xml:space="preserve">Skovbrynet 8</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">719209, 8934795</t>
+          <t xml:space="preserve">9604965</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="H70">
-        <v>296</v>
+        <v>622</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindeboder 20</t>
+          <t xml:space="preserve">Smedegade 21</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4241,16 +4241,16 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">719209, 8934795</t>
+          <t xml:space="preserve">1352516</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H71">
-        <v>318</v>
+        <v>590</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darupvej 52</t>
+          <t xml:space="preserve">Sognevej 4B</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4301,16 +4301,16 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">719219, 5307564</t>
+          <t xml:space="preserve">2171273</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H72">
-        <v>3050</v>
+        <v>300</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4351,17 +4351,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandgade 12</t>
+          <t xml:space="preserve">Spraglehøjvej 3</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">719262, 9232188</t>
+          <t xml:space="preserve">100043785</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="H73">
-        <v>440</v>
+        <v>283</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eriksvej 50B</t>
+          <t xml:space="preserve">Store Valbyvej 150</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">719268, 5308429</t>
+          <t xml:space="preserve">2174609</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="H74">
-        <v>266</v>
+        <v>313</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4471,26 +4471,26 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planetvej 30B</t>
+          <t xml:space="preserve">Store Valbyvej 248D</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">719295, 8907547</t>
+          <t xml:space="preserve">7343272</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H75">
-        <v>294</v>
+        <v>1379</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4531,26 +4531,26 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 4B</t>
+          <t xml:space="preserve">Strandgade 12</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">719337, 9604964</t>
+          <t xml:space="preserve">719262, 9232188</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H76">
-        <v>662</v>
+        <v>440</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Store Valbyvej 248D</t>
+          <t xml:space="preserve">Stændertorvet 19</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">7343272</t>
+          <t xml:space="preserve">5305072</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="H77">
-        <v>1379</v>
+        <v>322</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethehåbsvej 68</t>
+          <t xml:space="preserve">Stændertorvet 1B</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4661,16 +4661,16 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">7969204</t>
+          <t xml:space="preserve">5304088</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H78">
-        <v>1000</v>
+        <v>852</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Absalonsgade 7B</t>
+          <t xml:space="preserve">Stærkendevej 13</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4721,16 +4721,16 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">8173183</t>
+          <t xml:space="preserve">2209116</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H79">
-        <v>1867</v>
+        <v>342</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Absalonsgade 3</t>
+          <t xml:space="preserve">Søndre Alle 5</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4781,16 +4781,16 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">8173183</t>
+          <t xml:space="preserve">100513824</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="H80">
-        <v>1260</v>
+        <v>280</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Absalonsgade 13</t>
+          <t xml:space="preserve">Søndre Alle 7</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4841,16 +4841,16 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">8173183</t>
+          <t xml:space="preserve">100513815</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="H81">
-        <v>1323</v>
+        <v>475</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Køgevej 5</t>
+          <t xml:space="preserve">Toftebakken 10</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4901,16 +4901,16 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">8245209</t>
+          <t xml:space="preserve">100078592</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H82">
-        <v>764</v>
+        <v>288</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rabalderstræde 10</t>
+          <t xml:space="preserve">Toftebakken 11</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4961,16 +4961,16 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">8377662</t>
+          <t xml:space="preserve">100078592</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H83">
-        <v>553</v>
+        <v>473</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peblingevej 2B</t>
+          <t xml:space="preserve">Toftebakken 9</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">8908094</t>
+          <t xml:space="preserve">100078592</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="H84">
-        <v>692</v>
+        <v>323</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -5071,26 +5071,26 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gulddyssevej 70</t>
+          <t xml:space="preserve">Tofthøjvej 11</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8919779</t>
+          <t xml:space="preserve">2217131</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H85">
-        <v>472</v>
+        <v>866</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmelev Bygade 22A</t>
+          <t xml:space="preserve">Vindeboder 20</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995636</t>
+          <t xml:space="preserve">719209, 8934795</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="H86">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -5191,17 +5191,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 8</t>
+          <t xml:space="preserve">Vindeboder 20</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">9604965</t>
+          <t xml:space="preserve">719209, 8934795</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="H87">
-        <v>622</v>
+        <v>296</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmelev Bygade 15</t>
+          <t xml:space="preserve">Vindeboder 20</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5261,16 +5261,16 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">9883833</t>
+          <t xml:space="preserve">719209, 8934795</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H88">
-        <v>378</v>
+        <v>318</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herregårdsvej 61</t>
+          <t xml:space="preserve">Ågerupvej 24</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">9888274</t>
+          <t xml:space="preserve">2167528</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="H89">
-        <v>1776</v>
+        <v>444</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herregårdsvej 61</t>
+          <t xml:space="preserve">Darupvej 50</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5381,30 +5381,30 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">9888274</t>
+          <t xml:space="preserve">8995819</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H90">
-        <v>788</v>
+        <v>1270</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200014099</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-05-27</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vor Frue Hovedgade 71</t>
+          <t xml:space="preserve">Sankt Hans Gade 4</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2170375</t>
+          <t xml:space="preserve">5304764</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5450,11 +5450,11 @@
         </is>
       </c>
       <c r="H91">
-        <v>290</v>
+        <v>709</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014100</t>
+          <t xml:space="preserve">200014102</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Hans Gade 4</t>
+          <t xml:space="preserve">Vor Frue Hovedgade 71</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304764</t>
+          <t xml:space="preserve">2170375</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5570,11 +5570,11 @@
         </is>
       </c>
       <c r="H93">
-        <v>709</v>
+        <v>290</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014102</t>
+          <t xml:space="preserve">200014100</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5611,17 +5611,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darupvej 50</t>
+          <t xml:space="preserve">Assendløsevejen 95</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995819</t>
+          <t xml:space="preserve">7516035</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5630,16 +5630,16 @@
         </is>
       </c>
       <c r="H94">
-        <v>1270</v>
+        <v>950</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014099</t>
+          <t xml:space="preserve">200016725</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-27</t>
+          <t xml:space="preserve">2019-07-01</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assendløsevejen 95</t>
+          <t xml:space="preserve">Isafjordvej 1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">7516035</t>
+          <t xml:space="preserve">8727425</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5930,16 +5930,16 @@
         </is>
       </c>
       <c r="H99">
-        <v>950</v>
+        <v>796</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016725</t>
+          <t xml:space="preserve">200017082</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-01</t>
+          <t xml:space="preserve">2019-07-07</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isafjordvej 1</t>
+          <t xml:space="preserve">Stormandshøjen 2</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">8727425</t>
+          <t xml:space="preserve">9977521</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5990,16 +5990,16 @@
         </is>
       </c>
       <c r="H100">
-        <v>796</v>
+        <v>940</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017082</t>
+          <t xml:space="preserve">200017379</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-07</t>
+          <t xml:space="preserve">2019-07-10</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stormandshøjen 2</t>
+          <t xml:space="preserve">Baunehøjvej 50</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">9977521</t>
+          <t xml:space="preserve">2175063</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6050,16 +6050,16 @@
         </is>
       </c>
       <c r="H101">
-        <v>940</v>
+        <v>470</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017379</t>
+          <t xml:space="preserve">200017872</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-10</t>
+          <t xml:space="preserve">2019-07-23</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsholt 238</t>
+          <t xml:space="preserve">Himmelev Sognevej 115</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172727</t>
+          <t xml:space="preserve">8288838</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6110,11 +6110,11 @@
         </is>
       </c>
       <c r="H102">
-        <v>747</v>
+        <v>586</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017861</t>
+          <t xml:space="preserve">200017864</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsholt 236</t>
+          <t xml:space="preserve">Ravnsholt 232</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172775</t>
+          <t xml:space="preserve">2172779</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6170,11 +6170,11 @@
         </is>
       </c>
       <c r="H103">
-        <v>598</v>
+        <v>703</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017862</t>
+          <t xml:space="preserve">200017863</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsholt 232</t>
+          <t xml:space="preserve">Ravnsholt 236</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172779</t>
+          <t xml:space="preserve">2172775</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6230,11 +6230,11 @@
         </is>
       </c>
       <c r="H104">
-        <v>703</v>
+        <v>598</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017863</t>
+          <t xml:space="preserve">200017862</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunehøjvej 50</t>
+          <t xml:space="preserve">Ravnsholt 238</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2175063</t>
+          <t xml:space="preserve">2172727</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6290,11 +6290,11 @@
         </is>
       </c>
       <c r="H105">
-        <v>470</v>
+        <v>747</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017872</t>
+          <t xml:space="preserve">200017861</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmelev Sognevej 115</t>
+          <t xml:space="preserve">Frederiksborgvej 9</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">8288838</t>
+          <t xml:space="preserve">5304267</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6350,16 +6350,16 @@
         </is>
       </c>
       <c r="H106">
-        <v>586</v>
+        <v>327</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017864</t>
+          <t xml:space="preserve">200017925</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-23</t>
+          <t xml:space="preserve">2019-07-24</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksborgvej 9</t>
+          <t xml:space="preserve">Rådmandshaven 10</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304267</t>
+          <t xml:space="preserve">8995859</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6470,16 +6470,16 @@
         </is>
       </c>
       <c r="H108">
-        <v>327</v>
+        <v>1843</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017925</t>
+          <t xml:space="preserve">200017965</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-24</t>
+          <t xml:space="preserve">2019-07-27</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådmandshaven 10</t>
+          <t xml:space="preserve">Eriksvej 23</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995859</t>
+          <t xml:space="preserve">8040594</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6530,16 +6530,16 @@
         </is>
       </c>
       <c r="H109">
-        <v>1843</v>
+        <v>750</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017965</t>
+          <t xml:space="preserve">200018664</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-27</t>
+          <t xml:space="preserve">2019-08-13</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastelsvej 2</t>
+          <t xml:space="preserve">Hyrdehøj 60</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304625</t>
+          <t xml:space="preserve">9113192</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6650,11 +6650,11 @@
         </is>
       </c>
       <c r="H111">
-        <v>847</v>
+        <v>590</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018662</t>
+          <t xml:space="preserve">200018667</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 104</t>
+          <t xml:space="preserve">Kastelsvej 2</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312134</t>
+          <t xml:space="preserve">5304625</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6710,11 +6710,11 @@
         </is>
       </c>
       <c r="H112">
-        <v>965</v>
+        <v>847</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018671</t>
+          <t xml:space="preserve">200018662</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eriksvej 23</t>
+          <t xml:space="preserve">Troldehøj 2</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040594</t>
+          <t xml:space="preserve">8995933</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6770,11 +6770,11 @@
         </is>
       </c>
       <c r="H113">
-        <v>750</v>
+        <v>872</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018664</t>
+          <t xml:space="preserve">200018666</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troldehøj 2</t>
+          <t xml:space="preserve">Vestergade 104</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995933</t>
+          <t xml:space="preserve">5312134</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6890,11 +6890,11 @@
         </is>
       </c>
       <c r="H115">
-        <v>872</v>
+        <v>965</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018666</t>
+          <t xml:space="preserve">200018671</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyrdehøj 60</t>
+          <t xml:space="preserve">Vestergade 17A</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">9113192</t>
+          <t xml:space="preserve">10036944</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6950,16 +6950,16 @@
         </is>
       </c>
       <c r="H116">
-        <v>590</v>
+        <v>899</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018667</t>
+          <t xml:space="preserve">200020248</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-13</t>
+          <t xml:space="preserve">2019-09-10</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 17A</t>
+          <t xml:space="preserve">Eriksvej 21</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">10036944</t>
+          <t xml:space="preserve">8225803</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7010,16 +7010,16 @@
         </is>
       </c>
       <c r="H117">
-        <v>899</v>
+        <v>414</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020248</t>
+          <t xml:space="preserve">200020461</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-10</t>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7051,17 +7051,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eriksvej 21</t>
+          <t xml:space="preserve">Baunegårdsvej 70</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">8225803</t>
+          <t xml:space="preserve">2178666</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7070,16 +7070,16 @@
         </is>
       </c>
       <c r="H118">
-        <v>414</v>
+        <v>479</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020461</t>
+          <t xml:space="preserve">200020771</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7111,17 +7111,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågeruphøj 2</t>
+          <t xml:space="preserve">Bodsbjerggårdsvej 48</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167811</t>
+          <t xml:space="preserve">2216626</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -7130,11 +7130,11 @@
         </is>
       </c>
       <c r="H119">
-        <v>372</v>
+        <v>555</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020826</t>
+          <t xml:space="preserve">200020779</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7171,17 +7171,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 19</t>
+          <t xml:space="preserve">Bueager 5</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2176798</t>
+          <t xml:space="preserve">2211212</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -7190,11 +7190,11 @@
         </is>
       </c>
       <c r="H120">
-        <v>253</v>
+        <v>372</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020773</t>
+          <t xml:space="preserve">200020775</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunegårdsvej 70</t>
+          <t xml:space="preserve">Bygaden 19</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2178666</t>
+          <t xml:space="preserve">2176798</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7250,11 +7250,11 @@
         </is>
       </c>
       <c r="H121">
-        <v>479</v>
+        <v>253</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020771</t>
+          <t xml:space="preserve">200020773</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngbakken 7</t>
+          <t xml:space="preserve">Dronning Margrethes Vej 39</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2180449</t>
+          <t xml:space="preserve">5304862</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -7310,11 +7310,11 @@
         </is>
       </c>
       <c r="H122">
-        <v>403</v>
+        <v>922</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020831</t>
+          <t xml:space="preserve">200020780</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7351,30 +7351,30 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bueager 5</t>
+          <t xml:space="preserve">Engbækvej 20</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211212</t>
+          <t xml:space="preserve">9808161</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H123">
-        <v>372</v>
+        <v>821</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020775</t>
+          <t xml:space="preserve">200020781</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7411,30 +7411,30 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 21</t>
+          <t xml:space="preserve">Lyngbakken 7</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213458</t>
+          <t xml:space="preserve">2180449</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H124">
-        <v>311</v>
+        <v>403</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020830</t>
+          <t xml:space="preserve">200020831</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7471,30 +7471,30 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bodsbjerggårdsvej 48</t>
+          <t xml:space="preserve">Ramsømaglevej 21</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216626</t>
+          <t xml:space="preserve">2213458</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H125">
-        <v>555</v>
+        <v>311</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020779</t>
+          <t xml:space="preserve">200020830</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7531,17 +7531,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Margrethes Vej 39</t>
+          <t xml:space="preserve">Skovbrynet 2</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304862</t>
+          <t xml:space="preserve">9044555</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7550,11 +7550,11 @@
         </is>
       </c>
       <c r="H126">
-        <v>922</v>
+        <v>1015</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020780</t>
+          <t xml:space="preserve">200020789</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7591,17 +7591,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wiemosen 1</t>
+          <t xml:space="preserve">Skovbrynet 6</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5310765</t>
+          <t xml:space="preserve">9604963</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -7610,11 +7610,11 @@
         </is>
       </c>
       <c r="H127">
-        <v>733</v>
+        <v>879</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020827</t>
+          <t xml:space="preserve">200020787</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørstedvej 61B</t>
+          <t xml:space="preserve">Wiemosen 1</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">7940083</t>
+          <t xml:space="preserve">5310765</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -7670,11 +7670,11 @@
         </is>
       </c>
       <c r="H128">
-        <v>601</v>
+        <v>733</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020777</t>
+          <t xml:space="preserve">200020827</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7711,17 +7711,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørstedvej 61A</t>
+          <t xml:space="preserve">Ågeruphøj 2</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948799</t>
+          <t xml:space="preserve">2167811</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -7730,11 +7730,11 @@
         </is>
       </c>
       <c r="H129">
-        <v>581</v>
+        <v>372</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020772</t>
+          <t xml:space="preserve">200020826</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7771,17 +7771,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 2</t>
+          <t xml:space="preserve">Ørstedvej 61A</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">9044555</t>
+          <t xml:space="preserve">8948799</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -7790,11 +7790,11 @@
         </is>
       </c>
       <c r="H130">
-        <v>1015</v>
+        <v>581</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020789</t>
+          <t xml:space="preserve">200020772</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -7831,17 +7831,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 6</t>
+          <t xml:space="preserve">Ørstedvej 61B</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">9604963</t>
+          <t xml:space="preserve">7940083</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -7850,11 +7850,11 @@
         </is>
       </c>
       <c r="H131">
-        <v>879</v>
+        <v>601</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020787</t>
+          <t xml:space="preserve">200020777</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engbækvej 20</t>
+          <t xml:space="preserve">Ravnsholt 234</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7901,25 +7901,25 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">9808161</t>
+          <t xml:space="preserve">2172733</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H132">
-        <v>821</v>
+        <v>407</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020781</t>
+          <t xml:space="preserve">200023413</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-21</t>
+          <t xml:space="preserve">2019-11-04</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsholt 234</t>
+          <t xml:space="preserve">Algade 31</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172733</t>
+          <t xml:space="preserve">2174559</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -7970,16 +7970,16 @@
         </is>
       </c>
       <c r="H133">
-        <v>407</v>
+        <v>611</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023413</t>
+          <t xml:space="preserve">200023817</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-04</t>
+          <t xml:space="preserve">2019-11-12</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8011,17 +8011,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Algade 31</t>
+          <t xml:space="preserve">Møllevej 6</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174559</t>
+          <t xml:space="preserve">7054261</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8030,11 +8030,11 @@
         </is>
       </c>
       <c r="H134">
-        <v>611</v>
+        <v>796</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023817</t>
+          <t xml:space="preserve">200023841</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snebærvej 16</t>
+          <t xml:space="preserve">Rypevej 2</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8081,20 +8081,20 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209470</t>
+          <t xml:space="preserve">5306607</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H135">
-        <v>795</v>
+        <v>423</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023864</t>
+          <t xml:space="preserve">200023835</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rypevej 2</t>
+          <t xml:space="preserve">Snebærvej 16</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8141,20 +8141,20 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306607</t>
+          <t xml:space="preserve">2209470</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H136">
-        <v>423</v>
+        <v>795</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023835</t>
+          <t xml:space="preserve">200023864</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8191,30 +8191,30 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 6</t>
+          <t xml:space="preserve">Æblehaven 78</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">7054261</t>
+          <t xml:space="preserve">719221</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="H137">
-        <v>796</v>
+        <v>482</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023841</t>
+          <t xml:space="preserve">200023819</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8251,35 +8251,35 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Æblehaven 78</t>
+          <t xml:space="preserve">Agerskellet 13</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">719221</t>
+          <t xml:space="preserve">7568845</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H138">
-        <v>482</v>
+        <v>354</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023819</t>
+          <t xml:space="preserve">200023910</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-12</t>
+          <t xml:space="preserve">2019-11-13</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8311,17 +8311,17 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agerskellet 13</t>
+          <t xml:space="preserve">Grantoften 3</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">7568845</t>
+          <t xml:space="preserve">2217322</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -8330,16 +8330,16 @@
         </is>
       </c>
       <c r="H139">
-        <v>354</v>
+        <v>293</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">200023910</t>
+          <t xml:space="preserve">200024857</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-13</t>
+          <t xml:space="preserve">2019-12-01</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grantoften 3</t>
+          <t xml:space="preserve">Grantoften 5</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8386,11 +8386,11 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H140">
-        <v>293</v>
+        <v>392</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -8431,30 +8431,30 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grantoften 5</t>
+          <t xml:space="preserve">Hyrdehøj 62</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217322</t>
+          <t xml:space="preserve">9113193</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H141">
-        <v>392</v>
+        <v>722</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024857</t>
+          <t xml:space="preserve">200024858</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyrdehøj 62</t>
+          <t xml:space="preserve">Dommervænget 30</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">9113193</t>
+          <t xml:space="preserve">5306255</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -8570,16 +8570,16 @@
         </is>
       </c>
       <c r="H143">
-        <v>722</v>
+        <v>1225</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024858</t>
+          <t xml:space="preserve">200024872</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-01</t>
+          <t xml:space="preserve">2019-12-02</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8611,17 +8611,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dommervænget 30</t>
+          <t xml:space="preserve">Bygaden 28</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306255</t>
+          <t xml:space="preserve">2178710</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -8630,16 +8630,16 @@
         </is>
       </c>
       <c r="H144">
-        <v>1225</v>
+        <v>263</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024872</t>
+          <t xml:space="preserve">200024953</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-02</t>
+          <t xml:space="preserve">2019-12-03</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 28</t>
+          <t xml:space="preserve">Gammel Darupvej 3</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2178710</t>
+          <t xml:space="preserve">5307880</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -8690,11 +8690,11 @@
         </is>
       </c>
       <c r="H145">
-        <v>263</v>
+        <v>1383</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024953</t>
+          <t xml:space="preserve">200024956</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Darupvej 3</t>
+          <t xml:space="preserve">Lysalleen 33</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307880</t>
+          <t xml:space="preserve">8717244</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -8750,11 +8750,11 @@
         </is>
       </c>
       <c r="H146">
-        <v>1383</v>
+        <v>1298</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024956</t>
+          <t xml:space="preserve">200024948</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lysalleen 33</t>
+          <t xml:space="preserve">Eriksvej 40C</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8801,25 +8801,25 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">8717244</t>
+          <t xml:space="preserve">5308364</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H147">
-        <v>1298</v>
+        <v>852</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024948</t>
+          <t xml:space="preserve">200024993</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-03</t>
+          <t xml:space="preserve">2019-12-04</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eriksvej 40C</t>
+          <t xml:space="preserve">Københavnsvej 106C</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8861,20 +8861,20 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308364</t>
+          <t xml:space="preserve">7896055</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H148">
-        <v>852</v>
+        <v>680</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024993</t>
+          <t xml:space="preserve">200024994</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 106C</t>
+          <t xml:space="preserve">Kamstrupsti 2</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8921,25 +8921,25 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">7896055</t>
+          <t xml:space="preserve">5308151</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H149">
-        <v>680</v>
+        <v>400</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024994</t>
+          <t xml:space="preserve">200027969</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-04</t>
+          <t xml:space="preserve">2020-02-11</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kamstrupsti 2</t>
+          <t xml:space="preserve">Svogerslev Hovedgade 70A</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8981,25 +8981,25 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308151</t>
+          <t xml:space="preserve">8995659</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H150">
-        <v>400</v>
+        <v>995</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027969</t>
+          <t xml:space="preserve">200030999</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-11</t>
+          <t xml:space="preserve">2020-05-03</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svogerslev Hovedgade 70A</t>
+          <t xml:space="preserve">Maglehøjen 6</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9041,25 +9041,25 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995659</t>
+          <t xml:space="preserve">5307587</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H151">
-        <v>995</v>
+        <v>1934</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030999</t>
+          <t xml:space="preserve">200038312</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-03</t>
+          <t xml:space="preserve">2020-10-01</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maglehøjen 6</t>
+          <t xml:space="preserve">Astersvej 9</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307587</t>
+          <t xml:space="preserve">5308975</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -9110,16 +9110,16 @@
         </is>
       </c>
       <c r="H152">
-        <v>1934</v>
+        <v>4292</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">200038312</t>
+          <t xml:space="preserve">200049549</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-01</t>
+          <t xml:space="preserve">2021-05-26</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Astersvej 9</t>
+          <t xml:space="preserve">Stændertorvet 1D</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308975</t>
+          <t xml:space="preserve">5304086</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -9170,16 +9170,16 @@
         </is>
       </c>
       <c r="H153">
-        <v>4292</v>
+        <v>1906</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">200049549</t>
+          <t xml:space="preserve">200050785</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-05-26</t>
+          <t xml:space="preserve">2021-06-29</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stændertorvet 1D</t>
+          <t xml:space="preserve">Mosestykket 21</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9221,25 +9221,25 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304086</t>
+          <t xml:space="preserve">2208892</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H154">
-        <v>1906</v>
+        <v>770</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">200050785</t>
+          <t xml:space="preserve">100235815</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-06-29</t>
+          <t xml:space="preserve">2021-08-03</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosestykket 21</t>
+          <t xml:space="preserve">Københavnsvej 266</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9281,25 +9281,25 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2208892</t>
+          <t xml:space="preserve">5307061</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H155">
-        <v>770</v>
+        <v>573</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">100235815</t>
+          <t xml:space="preserve">200057196</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-03</t>
+          <t xml:space="preserve">2022-02-06</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 266</t>
+          <t xml:space="preserve">Møllehusvej 13</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307061</t>
+          <t xml:space="preserve">8135053</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -9350,16 +9350,16 @@
         </is>
       </c>
       <c r="H156">
-        <v>573</v>
+        <v>9546</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057196</t>
+          <t xml:space="preserve">200057529</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-06</t>
+          <t xml:space="preserve">2022-02-20</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllehusvej 13</t>
+          <t xml:space="preserve">Herregårdsvej 42</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">8135053</t>
+          <t xml:space="preserve">2172718</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -9410,16 +9410,16 @@
         </is>
       </c>
       <c r="H157">
-        <v>9546</v>
+        <v>1898</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057529</t>
+          <t xml:space="preserve">200057621</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-20</t>
+          <t xml:space="preserve">2022-02-23</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -9451,17 +9451,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herregårdsvej 42</t>
+          <t xml:space="preserve">Tranevej 7</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172718</t>
+          <t xml:space="preserve">7938930</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -9470,16 +9470,16 @@
         </is>
       </c>
       <c r="H158">
-        <v>1898</v>
+        <v>638</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057621</t>
+          <t xml:space="preserve">200060567</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-23</t>
+          <t xml:space="preserve">2022-06-29</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tranevej 7</t>
+          <t xml:space="preserve">Baunegårdsvej 80</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9521,25 +9521,25 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">7938930</t>
+          <t xml:space="preserve">2179645</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H159">
-        <v>638</v>
+        <v>677</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">200060567</t>
+          <t xml:space="preserve">311052501</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-06-29</t>
+          <t xml:space="preserve">2024-05-06</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -9571,35 +9571,35 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunegårdsvej 80</t>
+          <t xml:space="preserve">Højbakken 2</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2179645</t>
+          <t xml:space="preserve">10229610</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H160">
-        <v>677</v>
+        <v>620</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311052501</t>
+          <t xml:space="preserve">311060924</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-05-06</t>
+          <t xml:space="preserve">2024-06-23</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -9646,11 +9646,11 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H161">
-        <v>620</v>
+        <v>1226</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -9691,35 +9691,35 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højbakken 2</t>
+          <t xml:space="preserve">Frederiksborgvej 561</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">10229610</t>
+          <t xml:space="preserve">2178448</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H162">
-        <v>1226</v>
+        <v>322</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311060924</t>
+          <t xml:space="preserve">311062021</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-06-23</t>
+          <t xml:space="preserve">2024-06-27</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -9751,35 +9751,35 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksborgvej 561</t>
+          <t xml:space="preserve">Baunehøjvej 5</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2178448</t>
+          <t xml:space="preserve">2174626</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H163">
-        <v>322</v>
+        <v>287</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311062021</t>
+          <t xml:space="preserve">311082107</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-06-27</t>
+          <t xml:space="preserve">2024-11-06</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunehøjvej 5</t>
+          <t xml:space="preserve">Henrik Nielsens Vej 43</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174626</t>
+          <t xml:space="preserve">5309424</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -9830,11 +9830,11 @@
         </is>
       </c>
       <c r="H164">
-        <v>287</v>
+        <v>2196</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311082107</t>
+          <t xml:space="preserve">311082106</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Henrik Nielsens Vej 43</t>
+          <t xml:space="preserve">Himmelev Bygade 22C</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9881,20 +9881,20 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5309424</t>
+          <t xml:space="preserve">8995636</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H165">
-        <v>2196</v>
+        <v>426</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311082106</t>
+          <t xml:space="preserve">311082104</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Himmelev Bygade 22C</t>
+          <t xml:space="preserve">Bistruphøj 2</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9941,25 +9941,25 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995636</t>
+          <t xml:space="preserve">5312115</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H166">
-        <v>426</v>
+        <v>1048</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311082104</t>
+          <t xml:space="preserve">311083539</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-06</t>
+          <t xml:space="preserve">2024-11-14</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsparken 1</t>
+          <t xml:space="preserve">Bistrupvænge 16</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10006,11 +10006,11 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">139</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="H167">
-        <v>20718</v>
+        <v>927</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrupvænge 16</t>
+          <t xml:space="preserve">Lindegårdsparken 1</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10066,11 +10066,11 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t xml:space="preserve">139</t>
         </is>
       </c>
       <c r="H168">
-        <v>927</v>
+        <v>20718</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistruphøj 2</t>
+          <t xml:space="preserve">Rønøs Alle 38</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10121,25 +10121,25 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312115</t>
+          <t xml:space="preserve">5308584</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H169">
-        <v>1048</v>
+        <v>497</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311083539</t>
+          <t xml:space="preserve">311091392</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-14</t>
+          <t xml:space="preserve">2025-01-16</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønøs Alle 38</t>
+          <t xml:space="preserve">Nygade 13</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10181,25 +10181,25 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308584</t>
+          <t xml:space="preserve">5312309</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H170">
-        <v>497</v>
+        <v>568</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311091392</t>
+          <t xml:space="preserve">311096313</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-01-16</t>
+          <t xml:space="preserve">2025-02-19</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 13</t>
+          <t xml:space="preserve">Nygade 14</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H171">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 14</t>
+          <t xml:space="preserve">Nygade 18</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H172">
@@ -10351,35 +10351,35 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 18</t>
+          <t xml:space="preserve">Rosenhaven 13</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312309</t>
+          <t xml:space="preserve">2177192</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H173">
-        <v>568</v>
+        <v>268</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311096313</t>
+          <t xml:space="preserve">311098182</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-02-19</t>
+          <t xml:space="preserve">2025-03-02</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -10411,35 +10411,35 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenhaven 13</t>
+          <t xml:space="preserve">Strandvejen 18</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2177192</t>
+          <t xml:space="preserve">2174669</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H174">
-        <v>268</v>
+        <v>401</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311098182</t>
+          <t xml:space="preserve">311101306</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-02</t>
+          <t xml:space="preserve">2025-03-17</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 18</t>
+          <t xml:space="preserve">Sankt Ols Stræde 5</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2174669</t>
+          <t xml:space="preserve">5303417</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -10490,16 +10490,16 @@
         </is>
       </c>
       <c r="H175">
-        <v>401</v>
+        <v>482</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311101306</t>
+          <t xml:space="preserve">311109494</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-17</t>
+          <t xml:space="preserve">2025-04-28</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Ols Stræde 5</t>
+          <t xml:space="preserve">Strandgade 2</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10541,25 +10541,25 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303417</t>
+          <t xml:space="preserve">5312664, 100884612</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H176">
-        <v>482</v>
+        <v>345</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311109494</t>
+          <t xml:space="preserve">311110647</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-28</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandgade 2</t>
+          <t xml:space="preserve">Lammegade 26</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10601,25 +10601,25 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312664, 100884612</t>
+          <t xml:space="preserve">5303695</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H177">
-        <v>345</v>
+        <v>667</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311110647</t>
+          <t xml:space="preserve">311112925</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lammegade 30</t>
+          <t xml:space="preserve">Lammegade 28</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10666,11 +10666,11 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H178">
-        <v>496</v>
+        <v>667</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lammegade 36</t>
+          <t xml:space="preserve">Lammegade 30</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10726,11 +10726,11 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H179">
-        <v>624</v>
+        <v>496</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lammegade 28</t>
+          <t xml:space="preserve">Lammegade 36</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10786,11 +10786,11 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H180">
-        <v>667</v>
+        <v>624</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lammegade 26</t>
+          <t xml:space="preserve">Vestergade 6A</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -10841,25 +10841,25 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303695</t>
+          <t xml:space="preserve">5312565</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H181">
-        <v>667</v>
+        <v>3282</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311112925</t>
+          <t xml:space="preserve">311115034</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-05-26</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 6A</t>
+          <t xml:space="preserve">Lyngbakken 1</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312565</t>
+          <t xml:space="preserve">7175316</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -10910,16 +10910,16 @@
         </is>
       </c>
       <c r="H182">
-        <v>3282</v>
+        <v>362</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311115034</t>
+          <t xml:space="preserve">311118205</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-26</t>
+          <t xml:space="preserve">2025-06-10</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngbakken 1</t>
+          <t xml:space="preserve">Navervej 16</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">7175316</t>
+          <t xml:space="preserve">2209531</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -11030,16 +11030,16 @@
         </is>
       </c>
       <c r="H184">
-        <v>362</v>
+        <v>1432</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311118205</t>
+          <t xml:space="preserve">311124782</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-10</t>
+          <t xml:space="preserve">2025-07-13</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -11086,11 +11086,11 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H185">
-        <v>1432</v>
+        <v>979</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Navervej 16</t>
+          <t xml:space="preserve">Rabalderstræde 16</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209531</t>
+          <t xml:space="preserve">719145, 100067704</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -11150,16 +11150,16 @@
         </is>
       </c>
       <c r="H186">
-        <v>979</v>
+        <v>3529</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311124782</t>
+          <t xml:space="preserve">311137096</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-13</t>
+          <t xml:space="preserve">2025-09-28</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rabalderstræde 16</t>
+          <t xml:space="preserve">Jernbanegade 21A</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11201,25 +11201,25 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">719145, 100067704</t>
+          <t xml:space="preserve">8995769</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H187">
-        <v>3529</v>
+        <v>1236</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311137096</t>
+          <t xml:space="preserve">311162791</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-28</t>
+          <t xml:space="preserve">2026-03-07</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 21A</t>
+          <t xml:space="preserve">Vestre Hedevej 32</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11261,35 +11261,35 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">8995769</t>
+          <t xml:space="preserve">719290, 100013803</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H188">
-        <v>1236</v>
+        <v>276</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311162791</t>
+          <t xml:space="preserve">311241595</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-07</t>
+          <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Hedevej 32</t>
+          <t xml:space="preserve">Basgangen 20</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11321,25 +11321,25 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">719290, 100013803</t>
+          <t xml:space="preserve">719167, 100093183</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">47</t>
         </is>
       </c>
       <c r="H189">
-        <v>276</v>
+        <v>2980</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311241595</t>
+          <t xml:space="preserve">311351867</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-19</t>
+          <t xml:space="preserve">2028-12-17</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Basgangen 20</t>
+          <t xml:space="preserve">Hyrdehøj Stræde 2</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11381,25 +11381,25 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">719167, 100093183</t>
+          <t xml:space="preserve">100122346</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H190">
-        <v>2980</v>
+        <v>9549</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311351867</t>
+          <t xml:space="preserve">311522399</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-17</t>
+          <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -11431,35 +11431,35 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyrdehøj Stræde 2</t>
+          <t xml:space="preserve">Søndergade 11</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">100122346</t>
+          <t xml:space="preserve">7855029</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H191">
-        <v>9549</v>
+        <v>1530</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522399</t>
+          <t xml:space="preserve">311552201</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2031-09-30</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -11491,35 +11491,35 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 11</t>
+          <t xml:space="preserve">Sandhøjsvej 4</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">7855029</t>
+          <t xml:space="preserve">1304635</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H192">
-        <v>1530</v>
+        <v>599</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311552201</t>
+          <t xml:space="preserve">311569226</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-30</t>
+          <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandhøjsvej 4</t>
+          <t xml:space="preserve">Ramsømaglevej 17B</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">1304635</t>
+          <t xml:space="preserve">9840711</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -11570,16 +11570,16 @@
         </is>
       </c>
       <c r="H193">
-        <v>599</v>
+        <v>1459</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569226</t>
+          <t xml:space="preserve">311570325</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-21</t>
+          <t xml:space="preserve">2032-01-03</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 17B</t>
+          <t xml:space="preserve">Ramsømaglevej 17D</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -11626,15 +11626,15 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H194">
-        <v>1459</v>
+        <v>355</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570325</t>
+          <t xml:space="preserve">311570327</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -11671,35 +11671,35 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 17D</t>
+          <t xml:space="preserve">Ejboparken 6</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">9840711</t>
+          <t xml:space="preserve">7174735</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H195">
-        <v>355</v>
+        <v>435</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311570327</t>
+          <t xml:space="preserve">311586207</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-03</t>
+          <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørhusene 61</t>
+          <t xml:space="preserve">Ejboparken 6B</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -11741,20 +11741,20 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312139</t>
+          <t xml:space="preserve">7174735</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H196">
-        <v>826</v>
+        <v>517</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311595512</t>
+          <t xml:space="preserve">311586207</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejboparken 6</t>
+          <t xml:space="preserve">Ejboparken 6B</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -11806,11 +11806,11 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H197">
-        <v>435</v>
+        <v>258</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejboparken 6B</t>
+          <t xml:space="preserve">Hørhusene 61</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -11921,20 +11921,20 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">7174735</t>
+          <t xml:space="preserve">5312139</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H199">
-        <v>517</v>
+        <v>826</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586207</t>
+          <t xml:space="preserve">311595512</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejboparken 6B</t>
+          <t xml:space="preserve">Københavnsvej 266C</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">7174735</t>
+          <t xml:space="preserve">5307061</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -11990,16 +11990,16 @@
         </is>
       </c>
       <c r="H200">
-        <v>258</v>
+        <v>322</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586207</t>
+          <t xml:space="preserve">311587049</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-17</t>
+          <t xml:space="preserve">2032-03-22</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -12031,35 +12031,35 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Københavnsvej 266C</t>
+          <t xml:space="preserve">Bueager 8</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4130</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">5307061</t>
+          <t xml:space="preserve">2211135</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H201">
-        <v>322</v>
+        <v>469</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587049</t>
+          <t xml:space="preserve">311608657</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-22</t>
+          <t xml:space="preserve">2032-06-17</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bueager 8</t>
+          <t xml:space="preserve">Bueager 2</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -12106,20 +12106,20 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H202">
-        <v>469</v>
+        <v>4564</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311608657</t>
+          <t xml:space="preserve">311610029</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-17</t>
+          <t xml:space="preserve">2032-06-23</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -12166,11 +12166,11 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H203">
-        <v>4564</v>
+        <v>2127</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -12226,11 +12226,11 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H204">
-        <v>2127</v>
+        <v>847</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -12331,35 +12331,35 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bueager 2</t>
+          <t xml:space="preserve">Køgevej 106</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">4130</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211135</t>
+          <t xml:space="preserve">5308417</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H206">
-        <v>847</v>
+        <v>1620</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311610029</t>
+          <t xml:space="preserve">311626283</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-23</t>
+          <t xml:space="preserve">2032-09-08</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -12391,35 +12391,35 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Køgevej 106</t>
+          <t xml:space="preserve">Snoldelev Bygade 21B</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5308417</t>
+          <t xml:space="preserve">2202050</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H207">
-        <v>1620</v>
+        <v>438</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626283</t>
+          <t xml:space="preserve">311633105</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-08</t>
+          <t xml:space="preserve">2032-10-04</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -12511,17 +12511,17 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snoldelev Bygade 21B</t>
+          <t xml:space="preserve">Vor Frue Hovedgade 67</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2202050</t>
+          <t xml:space="preserve">8016122</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -12530,16 +12530,16 @@
         </is>
       </c>
       <c r="H209">
-        <v>438</v>
+        <v>2104</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311633114</t>
+          <t xml:space="preserve">311645050</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-04</t>
+          <t xml:space="preserve">2032-11-08</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -12571,7 +12571,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vor Frue Hovedgade 67</t>
+          <t xml:space="preserve">Vor Frue Hovedgade 67B</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -12586,11 +12586,11 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H210">
-        <v>2104</v>
+        <v>434</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vor Frue Hovedgade 67B</t>
+          <t xml:space="preserve">Vindeboder 12</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -12641,25 +12641,25 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">8016122</t>
+          <t xml:space="preserve">8934798</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H211">
-        <v>434</v>
+        <v>1378</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645050</t>
+          <t xml:space="preserve">311642567</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-08</t>
+          <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindeboder 12</t>
+          <t xml:space="preserve">Gundsølillevej 2</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -12701,7 +12701,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">8934798</t>
+          <t xml:space="preserve">2167605</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -12710,16 +12710,16 @@
         </is>
       </c>
       <c r="H212">
-        <v>1378</v>
+        <v>979</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311642567</t>
+          <t xml:space="preserve">311643576</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-15</t>
+          <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gundsølillevej 2</t>
+          <t xml:space="preserve">Gundsølillevej 6</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -12766,15 +12766,15 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H213">
-        <v>979</v>
+        <v>4101</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643576</t>
+          <t xml:space="preserve">311643577</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gundsølillevej 6</t>
+          <t xml:space="preserve">Sognevej 50</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -12821,25 +12821,25 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2167605</t>
+          <t xml:space="preserve">2172270</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H214">
-        <v>4101</v>
+        <v>3519</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643577</t>
+          <t xml:space="preserve">311644570</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2032-11-23</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -12871,17 +12871,17 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sognevej 50</t>
+          <t xml:space="preserve">Planetvej 30</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4040</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172270</t>
+          <t xml:space="preserve">8907547</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -12890,16 +12890,16 @@
         </is>
       </c>
       <c r="H215">
-        <v>3519</v>
+        <v>897</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644570</t>
+          <t xml:space="preserve">311644810</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-23</t>
+          <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -12946,11 +12946,11 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H216">
-        <v>897</v>
+        <v>398</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -13006,11 +13006,11 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H217">
-        <v>398</v>
+        <v>1311</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -13066,11 +13066,11 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H218">
-        <v>1311</v>
+        <v>924</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -13126,11 +13126,11 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H219">
-        <v>924</v>
+        <v>487</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -13186,11 +13186,11 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H220">
-        <v>487</v>
+        <v>256</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H221">
@@ -13306,11 +13306,11 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H222">
-        <v>256</v>
+        <v>897</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -13366,11 +13366,11 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="H223">
-        <v>897</v>
+        <v>983</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -13426,11 +13426,11 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="H224">
-        <v>983</v>
+        <v>552</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -13486,11 +13486,11 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H225">
-        <v>552</v>
+        <v>897</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H226">
@@ -13606,11 +13606,11 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H227">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
@@ -13666,11 +13666,11 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H228">
-        <v>898</v>
+        <v>280</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
@@ -13726,11 +13726,11 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H229">
-        <v>280</v>
+        <v>900</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
@@ -13786,11 +13786,11 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H230">
-        <v>900</v>
+        <v>789</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
@@ -13831,35 +13831,35 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planetvej 30</t>
+          <t xml:space="preserve">H H Kochs Vej 4</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t xml:space="preserve">4040</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">8907547</t>
+          <t xml:space="preserve">2173007</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H231">
-        <v>789</v>
+        <v>7796</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644810</t>
+          <t xml:space="preserve">311645058</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-24</t>
+          <t xml:space="preserve">2032-11-25</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">H H Kochs Vej 4</t>
+          <t xml:space="preserve">Skolevej 3</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -13901,7 +13901,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2173007</t>
+          <t xml:space="preserve">2180519</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -13910,11 +13910,11 @@
         </is>
       </c>
       <c r="H232">
-        <v>7796</v>
+        <v>1448</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645058</t>
+          <t xml:space="preserve">311644999</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -13966,11 +13966,11 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H233">
-        <v>1448</v>
+        <v>413</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 3</t>
+          <t xml:space="preserve">Lindelunden 1</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -14021,7 +14021,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2180519</t>
+          <t xml:space="preserve">5306821</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -14030,16 +14030,16 @@
         </is>
       </c>
       <c r="H234">
-        <v>413</v>
+        <v>5829</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644999</t>
+          <t xml:space="preserve">311645727</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-25</t>
+          <t xml:space="preserve">2032-11-29</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -14131,35 +14131,35 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindelunden 1</t>
+          <t xml:space="preserve">Ramsømaglevej 19</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4621</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">5306821</t>
+          <t xml:space="preserve">2213437</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H236">
-        <v>5829</v>
+        <v>2744</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645727</t>
+          <t xml:space="preserve">311646168</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-29</t>
+          <t xml:space="preserve">2032-11-30</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -14206,15 +14206,15 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H237">
-        <v>2744</v>
+        <v>1287</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646168</t>
+          <t xml:space="preserve">311646167</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -14251,35 +14251,35 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsømaglevej 19</t>
+          <t xml:space="preserve">Gammel Vindingevej 10</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t xml:space="preserve">4621</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213437</t>
+          <t xml:space="preserve">2209330</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H238">
-        <v>1287</v>
+        <v>5956</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646167</t>
+          <t xml:space="preserve">311646682</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-30</t>
+          <t xml:space="preserve">2032-12-02</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -14326,15 +14326,15 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H239">
-        <v>5956</v>
+        <v>447</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646682</t>
+          <t xml:space="preserve">311646683</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Vindingevej 10</t>
+          <t xml:space="preserve">Margrethekær 2</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -14381,25 +14381,25 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209330</t>
+          <t xml:space="preserve">9700889</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H240">
-        <v>447</v>
+        <v>2442</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646684</t>
+          <t xml:space="preserve">311647649</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-02</t>
+          <t xml:space="preserve">2032-12-07</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 2</t>
+          <t xml:space="preserve">Margrethekær 10</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -14446,20 +14446,20 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H241">
-        <v>2442</v>
+        <v>1500</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647649</t>
+          <t xml:space="preserve">311647742</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-07</t>
+          <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margrethekær 10</t>
+          <t xml:space="preserve">Hyrdehøj 3</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -14741,25 +14741,25 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">9700889</t>
+          <t xml:space="preserve">7713101</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H246">
-        <v>1500</v>
+        <v>11744</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647742</t>
+          <t xml:space="preserve">311649946</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-08</t>
+          <t xml:space="preserve">2032-12-17</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -14806,20 +14806,20 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H247">
-        <v>11744</v>
+        <v>1185</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649946</t>
+          <t xml:space="preserve">311649970</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-17</t>
+          <t xml:space="preserve">2032-12-18</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -14851,7 +14851,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyrdehøj 3</t>
+          <t xml:space="preserve">Møllehusvej 118</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -14861,25 +14861,25 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">7713101</t>
+          <t xml:space="preserve">258624, 258625</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H248">
-        <v>1185</v>
+        <v>4232</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649970</t>
+          <t xml:space="preserve">311650857</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-18</t>
+          <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebjergvej 8</t>
+          <t xml:space="preserve">Kirkebjergvej 6</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -15046,15 +15046,15 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H251">
-        <v>610</v>
+        <v>2239</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652565</t>
+          <t xml:space="preserve">311652567</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebjergvej 6</t>
+          <t xml:space="preserve">Kirkebjergvej 8</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -15106,15 +15106,15 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H252">
-        <v>2239</v>
+        <v>610</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652567</t>
+          <t xml:space="preserve">311652565</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusbuen 1</t>
+          <t xml:space="preserve">Gormsvej 9B</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -15586,15 +15586,15 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H260">
-        <v>9084</v>
+        <v>440</v>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656783</t>
+          <t xml:space="preserve">311656782</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -15631,7 +15631,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gormsvej 9B</t>
+          <t xml:space="preserve">Rådhusbuen 1</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -15646,15 +15646,15 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H261">
-        <v>440</v>
+        <v>9084</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656782</t>
+          <t xml:space="preserve">311656783</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -15751,7 +15751,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Ols Stræde 3</t>
+          <t xml:space="preserve">Munkebro 2</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -15766,15 +15766,15 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H263">
-        <v>858</v>
+        <v>608</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657451</t>
+          <t xml:space="preserve">311657447</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -15826,15 +15826,15 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H264">
-        <v>433</v>
+        <v>858</v>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657451</t>
+          <t xml:space="preserve">311657449</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -15871,7 +15871,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Munkebro 2</t>
+          <t xml:space="preserve">Sankt Ols Stræde 3</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -15886,15 +15886,15 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H265">
-        <v>608</v>
+        <v>433</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657451</t>
+          <t xml:space="preserve">311657448</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -15931,7 +15931,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Absalonsgade 2</t>
+          <t xml:space="preserve">Absalonsgade 1</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -15946,11 +15946,11 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H266">
-        <v>6187</v>
+        <v>378</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Absalonsgade 1</t>
+          <t xml:space="preserve">Absalonsgade 2</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -16006,11 +16006,11 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H267">
-        <v>378</v>
+        <v>6187</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynghøjen 107C</t>
+          <t xml:space="preserve">Lynghøjen 107B</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -16486,11 +16486,11 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H275">
-        <v>433</v>
+        <v>1552</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lynghøjen 107B</t>
+          <t xml:space="preserve">Lynghøjen 107C</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -16546,11 +16546,11 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H276">
-        <v>1552</v>
+        <v>433</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helligkorsvej 42C</t>
+          <t xml:space="preserve">Helligkorsvej 42A</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -16786,11 +16786,11 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H280">
-        <v>778</v>
+        <v>6340</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -16846,11 +16846,11 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H281">
-        <v>6340</v>
+        <v>2165</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helligkorsvej 42A</t>
+          <t xml:space="preserve">Helligkorsvej 42C</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -16906,11 +16906,11 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H282">
-        <v>2165</v>
+        <v>778</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ollerupvej 7</t>
+          <t xml:space="preserve">Ollerupvej 5</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -17026,11 +17026,11 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H284">
-        <v>826</v>
+        <v>494</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ollerupvej 5</t>
+          <t xml:space="preserve">Ollerupvej 7</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -17086,11 +17086,11 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H285">
-        <v>494</v>
+        <v>826</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670925</t>
+          <t xml:space="preserve">311670922</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670925</t>
+          <t xml:space="preserve">311670922</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -17251,7 +17251,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Vindingevej 221C</t>
+          <t xml:space="preserve">Østre Vindingevej 221A</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -17266,15 +17266,15 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H288">
-        <v>2100</v>
+        <v>766</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670925</t>
+          <t xml:space="preserve">311670922</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -17311,7 +17311,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Vindingevej 221A</t>
+          <t xml:space="preserve">Østre Vindingevej 221C</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -17326,15 +17326,15 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H289">
-        <v>766</v>
+        <v>2100</v>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670925</t>
+          <t xml:space="preserve">311670926</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrup Bakke 7</t>
+          <t xml:space="preserve">Bistrup Bakke 3</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -17446,15 +17446,15 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="H291">
-        <v>1077</v>
+        <v>997</v>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">311675950</t>
+          <t xml:space="preserve">311675948</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bistrup Bakke 3</t>
+          <t xml:space="preserve">Bistrup Bakke 7</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -17506,15 +17506,15 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="H292">
-        <v>997</v>
+        <v>1077</v>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">311675948</t>
+          <t xml:space="preserve">311675950</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -18211,7 +18211,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trekroner Alle 1C</t>
+          <t xml:space="preserve">Trekroner Alle 1</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -18226,15 +18226,15 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H304">
-        <v>2011</v>
+        <v>929</v>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725438</t>
+          <t xml:space="preserve">311725437</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
@@ -18286,11 +18286,11 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H305">
-        <v>929</v>
+        <v>553</v>
       </c>
       <c r="I305" t="inlineStr">
         <is>
@@ -18346,11 +18346,11 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H306">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -18406,15 +18406,15 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H307">
-        <v>548</v>
+        <v>599</v>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725437</t>
+          <t xml:space="preserve">311725441</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
@@ -18466,15 +18466,15 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H308">
-        <v>599</v>
+        <v>715</v>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725441</t>
+          <t xml:space="preserve">311725437</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
@@ -18511,7 +18511,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trekroner Alle 1</t>
+          <t xml:space="preserve">Trekroner Alle 1C</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -18526,15 +18526,15 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H309">
-        <v>715</v>
+        <v>2011</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725437</t>
+          <t xml:space="preserve">311725438</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
@@ -19134,7 +19134,7 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842232</t>
+          <t xml:space="preserve">311842230</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
@@ -19231,7 +19231,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringstedgade 22</t>
+          <t xml:space="preserve">Bredgade 17B</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -19241,7 +19241,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">10239664</t>
+          <t xml:space="preserve">5303694</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -19250,11 +19250,11 @@
         </is>
       </c>
       <c r="H321">
-        <v>300</v>
+        <v>982</v>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848392</t>
+          <t xml:space="preserve">311848390</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 17B</t>
+          <t xml:space="preserve">Ringstedgade 16</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -19301,7 +19301,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303694</t>
+          <t xml:space="preserve">5303892</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -19310,11 +19310,11 @@
         </is>
       </c>
       <c r="H322">
-        <v>982</v>
+        <v>938</v>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848390</t>
+          <t xml:space="preserve">311848394</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
@@ -19351,7 +19351,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringstedgade 16</t>
+          <t xml:space="preserve">Ringstedgade 22</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -19361,7 +19361,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">5303892</t>
+          <t xml:space="preserve">10239664</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -19370,11 +19370,11 @@
         </is>
       </c>
       <c r="H323">
-        <v>938</v>
+        <v>300</v>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848394</t>
+          <t xml:space="preserve">311848392</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">

--- a/public/exports/29189404.xlsx
+++ b/public/exports/29189404.xlsx
@@ -12414,7 +12414,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311633105</t>
+          <t xml:space="preserve">311633114</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646682</t>
+          <t xml:space="preserve">311646684</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646683</t>
+          <t xml:space="preserve">311646684</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -17154,7 +17154,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670922</t>
+          <t xml:space="preserve">311670925</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -17214,7 +17214,7 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670922</t>
+          <t xml:space="preserve">311670925</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670922</t>
+          <t xml:space="preserve">311670925</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -17334,7 +17334,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670926</t>
+          <t xml:space="preserve">311670925</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -19134,7 +19134,7 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842230</t>
+          <t xml:space="preserve">311842232</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">

--- a/public/exports/29189404.xlsx
+++ b/public/exports/29189404.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L328"/>
+  <dimension ref="A1:M328"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2164,10 +2339,15 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2224,10 +2404,15 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2284,10 +2469,15 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2344,10 +2534,15 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2404,10 +2599,15 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2464,10 +2664,15 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2524,10 +2729,15 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2584,10 +2794,15 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2644,10 +2859,15 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2704,10 +2924,15 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2764,10 +2989,15 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2824,10 +3054,15 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2884,10 +3119,15 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2944,10 +3184,15 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3004,10 +3249,15 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3064,10 +3314,15 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3124,10 +3379,15 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3184,10 +3444,15 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3244,10 +3509,15 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3304,10 +3574,15 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3364,10 +3639,15 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3424,10 +3704,15 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3484,10 +3769,15 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3544,10 +3834,15 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3604,10 +3899,15 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3664,10 +3964,15 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3724,10 +4029,15 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3784,10 +4094,15 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3844,10 +4159,15 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3904,10 +4224,15 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3964,10 +4289,15 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4024,10 +4354,15 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4084,10 +4419,15 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4144,10 +4484,15 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4204,10 +4549,15 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4264,10 +4614,15 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4324,10 +4679,15 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4384,10 +4744,15 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4444,10 +4809,15 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4504,10 +4874,15 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4564,10 +4939,15 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4624,10 +5004,15 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4684,10 +5069,15 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4744,10 +5134,15 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4804,10 +5199,15 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4864,10 +5264,15 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4924,10 +5329,15 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4984,10 +5394,15 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5044,10 +5459,15 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5104,10 +5524,15 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5164,10 +5589,15 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5224,10 +5654,15 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5284,10 +5719,15 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5344,10 +5784,15 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">BALSLEV</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-05-27</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">BALSLEV</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-05-27</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">BALSLEV</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-05-27</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">BALSLEV</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-05-27</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-01</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-01</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-01</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-01</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-01</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">BALSLEV</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-07</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">BALSLEV</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-10</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">BALSLEV</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-23</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">BALSLEV</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-23</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">BALSLEV</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-23</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">BALSLEV</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-23</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">BALSLEV</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-23</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">BALSLEV</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-24</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">BALSLEV</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-24</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="L107" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">BALSLEV</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-27</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="L108" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-13</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="L109" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-13</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-13</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="L111" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-13</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
+      <c r="L112" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-13</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
+      <c r="L113" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-13</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="L114" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-13</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="L115" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-10</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="L116" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="L118" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
+      <c r="L120" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
+      <c r="L121" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
+      <c r="L122" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
+      <c r="L123" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
+      <c r="L124" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
+      <c r="L125" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
+      <c r="L126" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
+      <c r="L127" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
+      <c r="L128" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
+      <c r="L129" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
+      <c r="L130" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
+      <c r="L131" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-04</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
+      <c r="L132" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-12</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
+      <c r="L133" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-12</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
+      <c r="L134" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-12</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
+      <c r="L135" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-12</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
+      <c r="L136" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-12</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
+      <c r="L137" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-13</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
+      <c r="L138" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-01</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
+      <c r="L139" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-01</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
+      <c r="L140" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr">
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-01</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
+      <c r="L141" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-01</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
+      <c r="L142" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-02</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
+      <c r="L143" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-03</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
+      <c r="L144" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-03</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
+      <c r="L145" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-03</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
+      <c r="L146" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr">
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-04</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
+      <c r="L147" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr">
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-04</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
+      <c r="L148" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-11</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
+      <c r="L149" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">BALSLEV</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-05-03</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
+      <c r="L150" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-10-01</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
+      <c r="L151" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr">
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-05-26</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
+      <c r="L152" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr">
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-06-29</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
+      <c r="L153" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-08-03</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
+      <c r="L154" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr">
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">Forum r.i.</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-02-06</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
+      <c r="L155" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr">
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">TopDahl ApS</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-02-20</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
+      <c r="L156" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">TopDahl ApS</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-02-23</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
+      <c r="L157" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-06-29</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
+      <c r="L158" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr">
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-05-06</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
+      <c r="L159" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr">
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-06-23</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
+      <c r="L160" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr">
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-06-23</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
+      <c r="L161" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-06-27</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
+      <c r="L162" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr">
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-11-06</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
+      <c r="L163" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-11-06</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
+      <c r="L164" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-11-06</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
+      <c r="L165" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr">
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-11-14</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
+      <c r="L166" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr">
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-11-14</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
+      <c r="L167" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr">
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-11-14</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
+      <c r="L168" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-01-16</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
+      <c r="L169" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr">
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-02-19</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
+      <c r="L170" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr">
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-02-19</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
+      <c r="L171" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr">
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-02-19</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
+      <c r="L172" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr">
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-03-02</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
+      <c r="L173" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr">
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-03-17</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
+      <c r="L174" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-04-28</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
+      <c r="L175" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
+      <c r="L176" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr">
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
+      <c r="L177" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr">
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
+      <c r="L178" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr">
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
+      <c r="L179" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr">
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
+      <c r="L180" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr">
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-05-26</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
+      <c r="L181" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr">
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-06-10</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
+      <c r="L182" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-06-10</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
+      <c r="L183" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr">
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-07-13</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
+      <c r="L184" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr">
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-07-13</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
+      <c r="L185" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr">
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">John Klysner Consult ApS</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-09-28</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
+      <c r="L186" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr">
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">Boligeftersyn P/S</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-07</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
+      <c r="L187" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr">
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
+      <c r="L188" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr">
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-12-17</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
+      <c r="L189" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L189" t="inlineStr">
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
+      <c r="L190" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L190" t="inlineStr">
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-09-30</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
+      <c r="L191" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr">
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
+      <c r="L192" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr">
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-03</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
+      <c r="L193" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr">
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-01-03</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
+      <c r="L194" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr">
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
+      <c r="L195" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr">
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
+      <c r="L196" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr">
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
+      <c r="L197" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr">
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
+      <c r="L198" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr">
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-17</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
+      <c r="L199" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr">
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-22</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
+      <c r="L200" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr">
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12054,20 +13054,25 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311608657</t>
+          <t xml:space="preserve">311608660</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Energi og bæredygtighed</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-17</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
+      <c r="L201" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr">
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Energi og bæredygtighed</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-23</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
+      <c r="L202" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr">
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Energi og bæredygtighed</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-23</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
+      <c r="L203" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L203" t="inlineStr">
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Energi og bæredygtighed</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-23</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
+      <c r="L204" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr">
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Energi og bæredygtighed</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-06-23</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
+      <c r="L205" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr">
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-08</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
+      <c r="L206" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr">
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-04</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
+      <c r="L207" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr">
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12479,15 +13514,20 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-04</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
+      <c r="L208" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr">
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12539,15 +13579,20 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-08</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
+      <c r="L209" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr">
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12599,15 +13644,20 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-08</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
+      <c r="L210" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12659,15 +13709,20 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-15</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
+      <c r="L211" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr">
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12719,15 +13774,20 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
+      <c r="L212" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr">
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12779,15 +13839,20 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
+      <c r="L213" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr">
+      <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12839,15 +13904,20 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-23</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
+      <c r="L214" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr">
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12899,15 +13969,20 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t xml:space="preserve">BOTJEK A/S</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
+      <c r="L215" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr">
+      <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12959,15 +14034,20 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t xml:space="preserve">BOTJEK A/S</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
+      <c r="L216" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr">
+      <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13019,15 +14099,20 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t xml:space="preserve">BOTJEK A/S</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
+      <c r="L217" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr">
+      <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13079,15 +14164,20 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t xml:space="preserve">BOTJEK A/S</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
+      <c r="L218" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L218" t="inlineStr">
+      <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13139,15 +14229,20 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t xml:space="preserve">BOTJEK A/S</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
+      <c r="L219" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr">
+      <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13199,15 +14294,20 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t xml:space="preserve">BOTJEK A/S</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
+      <c r="L220" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr">
+      <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13259,15 +14359,20 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
+          <t xml:space="preserve">BOTJEK A/S</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
+      <c r="L221" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L221" t="inlineStr">
+      <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13319,15 +14424,20 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
+          <t xml:space="preserve">BOTJEK A/S</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
+      <c r="L222" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr">
+      <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13379,15 +14489,20 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
+          <t xml:space="preserve">BOTJEK A/S</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
+      <c r="L223" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr">
+      <c r="M223" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13439,15 +14554,20 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
+          <t xml:space="preserve">BOTJEK A/S</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
+      <c r="L224" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr">
+      <c r="M224" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13499,15 +14619,20 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
+          <t xml:space="preserve">BOTJEK A/S</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
+      <c r="L225" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L225" t="inlineStr">
+      <c r="M225" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13559,15 +14684,20 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
+          <t xml:space="preserve">BOTJEK A/S</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
+      <c r="L226" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr">
+      <c r="M226" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13619,15 +14749,20 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
+          <t xml:space="preserve">BOTJEK A/S</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
+      <c r="L227" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L227" t="inlineStr">
+      <c r="M227" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13679,15 +14814,20 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
+          <t xml:space="preserve">BOTJEK A/S</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
+      <c r="L228" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr">
+      <c r="M228" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13739,15 +14879,20 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
+          <t xml:space="preserve">BOTJEK A/S</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
+      <c r="L229" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L229" t="inlineStr">
+      <c r="M229" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13799,15 +14944,20 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
+          <t xml:space="preserve">BOTJEK A/S</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-24</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
+      <c r="L230" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L230" t="inlineStr">
+      <c r="M230" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13859,15 +15009,20 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-25</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
+      <c r="L231" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L231" t="inlineStr">
+      <c r="M231" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13919,15 +15074,20 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-25</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
+      <c r="L232" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L232" t="inlineStr">
+      <c r="M232" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13979,15 +15139,20 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-25</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
+      <c r="L233" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L233" t="inlineStr">
+      <c r="M233" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14039,15 +15204,20 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-29</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
+      <c r="L234" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L234" t="inlineStr">
+      <c r="M234" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14099,15 +15269,20 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-29</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
+      <c r="L235" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L235" t="inlineStr">
+      <c r="M235" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14159,15 +15334,20 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-30</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
+      <c r="L236" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L236" t="inlineStr">
+      <c r="M236" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14219,15 +15399,20 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-30</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
+      <c r="L237" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L237" t="inlineStr">
+      <c r="M237" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14274,20 +15459,25 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646684</t>
+          <t xml:space="preserve">311646682</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-02</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
+      <c r="L238" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L238" t="inlineStr">
+      <c r="M238" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14334,20 +15524,25 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646684</t>
+          <t xml:space="preserve">311646683</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-02</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
+      <c r="L239" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L239" t="inlineStr">
+      <c r="M239" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14399,15 +15594,20 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-07</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
+      <c r="L240" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L240" t="inlineStr">
+      <c r="M240" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14459,15 +15659,20 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr">
+      <c r="L241" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L241" t="inlineStr">
+      <c r="M241" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14519,15 +15724,20 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
+      <c r="L242" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L242" t="inlineStr">
+      <c r="M242" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14579,15 +15789,20 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
+      <c r="L243" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L243" t="inlineStr">
+      <c r="M243" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14639,15 +15854,20 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr">
+      <c r="L244" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L244" t="inlineStr">
+      <c r="M244" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14699,15 +15919,20 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr">
+      <c r="L245" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L245" t="inlineStr">
+      <c r="M245" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14759,15 +15984,20 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-17</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
+      <c r="L246" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L246" t="inlineStr">
+      <c r="M246" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14819,15 +16049,20 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-18</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr">
+      <c r="L247" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L247" t="inlineStr">
+      <c r="M247" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14879,15 +16114,20 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-12-21</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr">
+      <c r="L248" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L248" t="inlineStr">
+      <c r="M248" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14939,15 +16179,20 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-05</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
+      <c r="L249" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L249" t="inlineStr">
+      <c r="M249" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14999,15 +16244,20 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-05</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr">
+      <c r="L250" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L250" t="inlineStr">
+      <c r="M250" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15059,15 +16309,20 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-05</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
+      <c r="L251" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr">
+      <c r="M251" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15119,15 +16374,20 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-05</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr">
+      <c r="L252" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L252" t="inlineStr">
+      <c r="M252" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15179,15 +16439,20 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-06</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr">
+      <c r="L253" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L253" t="inlineStr">
+      <c r="M253" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15239,15 +16504,20 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-09</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr">
+      <c r="L254" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L254" t="inlineStr">
+      <c r="M254" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15299,15 +16569,20 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-09</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr">
+      <c r="L255" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L255" t="inlineStr">
+      <c r="M255" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15359,15 +16634,20 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-09</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr">
+      <c r="L256" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L256" t="inlineStr">
+      <c r="M256" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15419,15 +16699,20 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-20</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr">
+      <c r="L257" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L257" t="inlineStr">
+      <c r="M257" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15479,15 +16764,20 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-23</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr">
+      <c r="L258" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L258" t="inlineStr">
+      <c r="M258" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15539,15 +16829,20 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-27</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr">
+      <c r="L259" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L259" t="inlineStr">
+      <c r="M259" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15599,15 +16894,20 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-30</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
+      <c r="L260" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L260" t="inlineStr">
+      <c r="M260" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15659,15 +16959,20 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-30</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
+      <c r="L261" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L261" t="inlineStr">
+      <c r="M261" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15719,15 +17024,20 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-31</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr">
+      <c r="L262" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L262" t="inlineStr">
+      <c r="M262" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15774,20 +17084,25 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657447</t>
+          <t xml:space="preserve">311657451</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-01</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
+      <c r="L263" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L263" t="inlineStr">
+      <c r="M263" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15834,20 +17149,25 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657449</t>
+          <t xml:space="preserve">311657451</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-01</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
+      <c r="L264" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L264" t="inlineStr">
+      <c r="M264" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15894,20 +17214,25 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657448</t>
+          <t xml:space="preserve">311657451</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-01</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr">
+      <c r="L265" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L265" t="inlineStr">
+      <c r="M265" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15959,15 +17284,20 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
+          <t xml:space="preserve">Inspec ApS</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr">
+      <c r="L266" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L266" t="inlineStr">
+      <c r="M266" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16019,15 +17349,20 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
+          <t xml:space="preserve">Inspec ApS</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr">
+      <c r="L267" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L267" t="inlineStr">
+      <c r="M267" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16079,15 +17414,20 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-14</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr">
+      <c r="L268" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L268" t="inlineStr">
+      <c r="M268" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16139,15 +17479,20 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-07</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr">
+      <c r="L269" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L269" t="inlineStr">
+      <c r="M269" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16199,15 +17544,20 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-07</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr">
+      <c r="L270" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L270" t="inlineStr">
+      <c r="M270" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16259,15 +17609,20 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-07</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr">
+      <c r="L271" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L271" t="inlineStr">
+      <c r="M271" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16319,15 +17674,20 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-07</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr">
+      <c r="L272" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L272" t="inlineStr">
+      <c r="M272" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16379,15 +17739,20 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-07</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr">
+      <c r="L273" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L273" t="inlineStr">
+      <c r="M273" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16439,15 +17804,20 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-10</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr">
+      <c r="L274" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L274" t="inlineStr">
+      <c r="M274" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16499,15 +17869,20 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-10</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr">
+      <c r="L275" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L275" t="inlineStr">
+      <c r="M275" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16559,15 +17934,20 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-10</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr">
+      <c r="L276" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L276" t="inlineStr">
+      <c r="M276" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16619,15 +17999,20 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-14</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr">
+      <c r="L277" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L277" t="inlineStr">
+      <c r="M277" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16679,15 +18064,20 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-15</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr">
+      <c r="L278" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L278" t="inlineStr">
+      <c r="M278" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16739,15 +18129,20 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr">
+      <c r="L279" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L279" t="inlineStr">
+      <c r="M279" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16799,15 +18194,20 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr">
+      <c r="L280" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L280" t="inlineStr">
+      <c r="M280" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16859,15 +18259,20 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr">
+      <c r="L281" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L281" t="inlineStr">
+      <c r="M281" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16919,15 +18324,20 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr">
+      <c r="L282" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L282" t="inlineStr">
+      <c r="M282" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16979,15 +18389,20 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr">
+      <c r="L283" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L283" t="inlineStr">
+      <c r="M283" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17039,15 +18454,20 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr">
+      <c r="L284" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L284" t="inlineStr">
+      <c r="M284" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17099,15 +18519,20 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr">
+      <c r="L285" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L285" t="inlineStr">
+      <c r="M285" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17159,15 +18584,20 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-31</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr">
+      <c r="L286" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L286" t="inlineStr">
+      <c r="M286" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17219,15 +18649,20 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-31</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr">
+      <c r="L287" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L287" t="inlineStr">
+      <c r="M287" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17279,15 +18714,20 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-31</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr">
+      <c r="L288" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L288" t="inlineStr">
+      <c r="M288" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17339,15 +18779,20 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-31</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr">
+      <c r="L289" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L289" t="inlineStr">
+      <c r="M289" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17399,15 +18844,20 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr">
+      <c r="L290" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L290" t="inlineStr">
+      <c r="M290" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17459,15 +18909,20 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-24</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr">
+      <c r="L291" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L291" t="inlineStr">
+      <c r="M291" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17519,15 +18974,20 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-24</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr">
+      <c r="L292" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L292" t="inlineStr">
+      <c r="M292" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17579,15 +19039,20 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr">
+      <c r="L293" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L293" t="inlineStr">
+      <c r="M293" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17639,15 +19104,20 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr">
+      <c r="L294" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L294" t="inlineStr">
+      <c r="M294" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17699,15 +19169,20 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-25</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr">
+      <c r="L295" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L295" t="inlineStr">
+      <c r="M295" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17759,15 +19234,20 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-08</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr">
+      <c r="L296" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L296" t="inlineStr">
+      <c r="M296" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17819,15 +19299,20 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-26</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr">
+      <c r="L297" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L297" t="inlineStr">
+      <c r="M297" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17879,15 +19364,20 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-26</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr">
+      <c r="L298" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L298" t="inlineStr">
+      <c r="M298" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17939,15 +19429,20 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-26</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr">
+      <c r="L299" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L299" t="inlineStr">
+      <c r="M299" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17999,15 +19494,20 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr">
+      <c r="L300" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L300" t="inlineStr">
+      <c r="M300" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18059,15 +19559,20 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr">
+      <c r="L301" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L301" t="inlineStr">
+      <c r="M301" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18119,15 +19624,20 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr">
+      <c r="L302" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L302" t="inlineStr">
+      <c r="M302" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18179,15 +19689,20 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr">
+      <c r="L303" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L303" t="inlineStr">
+      <c r="M303" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18239,15 +19754,20 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr">
+      <c r="L304" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L304" t="inlineStr">
+      <c r="M304" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18299,15 +19819,20 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr">
+      <c r="L305" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L305" t="inlineStr">
+      <c r="M305" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18359,15 +19884,20 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr">
+      <c r="L306" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L306" t="inlineStr">
+      <c r="M306" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18419,15 +19949,20 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr">
+      <c r="L307" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L307" t="inlineStr">
+      <c r="M307" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18479,15 +20014,20 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr">
+      <c r="L308" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L308" t="inlineStr">
+      <c r="M308" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18539,15 +20079,20 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr">
+      <c r="L309" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L309" t="inlineStr">
+      <c r="M309" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18599,15 +20144,20 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kelstrupgaard VVS &amp; Ingeniør ApS</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-07</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr">
+      <c r="L310" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L310" t="inlineStr">
+      <c r="M310" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18659,15 +20209,20 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
+          <t xml:space="preserve">Norca Aps</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-26</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr">
+      <c r="L311" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L311" t="inlineStr">
+      <c r="M311" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18719,15 +20274,20 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
+          <t xml:space="preserve">Norca Aps</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-26</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr">
+      <c r="L312" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L312" t="inlineStr">
+      <c r="M312" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18779,15 +20339,20 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
+          <t xml:space="preserve">Norca Aps</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-26</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr">
+      <c r="L313" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L313" t="inlineStr">
+      <c r="M313" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18839,15 +20404,20 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
+          <t xml:space="preserve">Norca Aps</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-09-26</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr">
+      <c r="L314" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L314" t="inlineStr">
+      <c r="M314" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18899,15 +20469,20 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-10-28</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr">
+      <c r="L315" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L315" t="inlineStr">
+      <c r="M315" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18959,15 +20534,20 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-25</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr">
+      <c r="L316" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L316" t="inlineStr">
+      <c r="M316" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19019,15 +20599,20 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
+          <t xml:space="preserve">Norca Aps</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr">
+      <c r="L317" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L317" t="inlineStr">
+      <c r="M317" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19079,15 +20664,20 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-06-04</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr">
+      <c r="L318" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L318" t="inlineStr">
+      <c r="M318" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19139,15 +20729,20 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-02</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr">
+      <c r="L319" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L319" t="inlineStr">
+      <c r="M319" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19199,15 +20794,20 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
+          <t xml:space="preserve">Norca Aps</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-24</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr">
+      <c r="L320" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L320" t="inlineStr">
+      <c r="M320" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19259,15 +20859,20 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
+          <t xml:space="preserve">Norca Aps</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-11</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr">
+      <c r="L321" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L321" t="inlineStr">
+      <c r="M321" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19319,15 +20924,20 @@
       </c>
       <c r="J322" t="inlineStr">
         <is>
+          <t xml:space="preserve">Norca Aps</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-11</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr">
+      <c r="L322" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L322" t="inlineStr">
+      <c r="M322" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19379,15 +20989,20 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
+          <t xml:space="preserve">Norca Aps</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-11</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr">
+      <c r="L323" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L323" t="inlineStr">
+      <c r="M323" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19439,15 +21054,20 @@
       </c>
       <c r="J324" t="inlineStr">
         <is>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-08-13</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr">
+      <c r="L324" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L324" t="inlineStr">
+      <c r="M324" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19499,15 +21119,20 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-27</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr">
+      <c r="L325" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L325" t="inlineStr">
+      <c r="M325" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19559,15 +21184,20 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-01-26</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr">
+      <c r="L326" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L326" t="inlineStr">
+      <c r="M326" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19619,15 +21249,20 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
+          <t xml:space="preserve">e-consult ApS</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-27</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr">
+      <c r="L327" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L327" t="inlineStr">
+      <c r="M327" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19679,21 +21314,26 @@
       </c>
       <c r="J328" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-09-01</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr">
+      <c r="L328" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L328" t="inlineStr">
+      <c r="M328" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L328"/>
+  <autoFilter ref="A1:M328"/>
 </worksheet>
 </file>
--- a/public/exports/29189404.xlsx
+++ b/public/exports/29189404.xlsx
@@ -13054,7 +13054,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311608660</t>
+          <t xml:space="preserve">311608657</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -13444,12 +13444,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311633114</t>
+          <t xml:space="preserve">311633105</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -16889,12 +16889,12 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656782</t>
+          <t xml:space="preserve">311656779</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656783</t>
+          <t xml:space="preserve">311656779</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -17084,12 +17084,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657451</t>
+          <t xml:space="preserve">311657447</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -17149,12 +17149,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657451</t>
+          <t xml:space="preserve">311657449</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -17214,12 +17214,12 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657451</t>
+          <t xml:space="preserve">311657448</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670925</t>
+          <t xml:space="preserve">311670922</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -18644,7 +18644,7 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670925</t>
+          <t xml:space="preserve">311670922</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -18709,7 +18709,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670925</t>
+          <t xml:space="preserve">311670922</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -20724,12 +20724,12 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311842232</t>
+          <t xml:space="preserve">311842230</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Topdahl Ingeniører og Arkitekter ApS</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
